--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -817,13 +817,13 @@
         <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -838,7 +838,7 @@
         <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -862,10 +862,10 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
         <v>6.8</v>
@@ -877,10 +877,10 @@
         <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV2" t="n">
         <v>8.800000000000001</v>
@@ -889,13 +889,13 @@
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
         <v>4.7</v>
@@ -916,11 +916,11 @@
         <v>4.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H8" t="n">
         <v>3.3</v>
@@ -1933,7 +1933,7 @@
         <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="K8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
         <v>7.8</v>
@@ -2321,7 +2321,7 @@
         <v>30</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2342,7 +2342,7 @@
         <v>1.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 00:47:30</t>
+          <t>2026-03-21 03:19:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
         <v>8.800000000000001</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>2.76</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
         <v>5.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
         <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="K8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 03:19:02</t>
+          <t>2026-03-21 05:50:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
         <v>4.3</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.76</v>
       </c>
       <c r="G11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H11" t="n">
         <v>2.48</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 05:50:37</t>
+          <t>2026-03-21 08:22:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 08:22:08</t>
+          <t>2026-03-21 10:53:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -757,28 +757,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -811,116 +811,116 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>4.7</v>
       </c>
       <c r="G3" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="I3" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>1.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>2.58</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
         <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
         <v>2.82</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
         <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="G10" t="n">
-        <v>1.61</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>1.14</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 10:53:35</t>
+          <t>2026-03-21 13:25:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
@@ -775,16 +775,16 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>1.7</v>
@@ -793,10 +793,10 @@
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,43 +805,43 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.7</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
@@ -1330,31 +1330,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>1.9</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
         <v>1.01</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>1.74</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,589 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 13:25:00</t>
+          <t>2026-03-21 15:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-21 15:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rubio Nu</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-21 15:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-21 15:54:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -766,7 +766,7 @@
         <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
@@ -781,10 +781,10 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.74</v>
+        <v>1.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
         <v>1.7</v>
@@ -793,10 +793,10 @@
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,7 +805,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W2" t="n">
         <v>1.31</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>4.9</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="I3" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.02</v>
       </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -1536,167 +1536,167 @@
         <v>4.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -2124,10 +2124,10 @@
         <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
         <v>3.2</v>
@@ -2148,7 +2148,7 @@
         <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="G11" t="n">
         <v>1.74</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q11" t="n">
         <v>2.32</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
@@ -2730,7 +2730,7 @@
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="H13" t="n">
         <v>2.62</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-21 15:54:37</t>
+          <t>2026-03-21 18:20:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -760,7 +760,7 @@
         <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="H2" t="n">
         <v>2.26</v>
@@ -781,10 +781,10 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
         <v>1.7</v>
@@ -793,10 +793,10 @@
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -808,119 +808,119 @@
         <v>1.67</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG2" t="n">
         <v>19.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="G3" t="n">
         <v>6.4</v>
@@ -981,7 +981,7 @@
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
         <v>2.36</v>
@@ -996,7 +996,7 @@
         <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
         <v>2.04</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G4" t="n">
         <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2.64</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>3.75</v>
@@ -1166,22 +1166,22 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
         <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
         <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
         <v>1.02</v>
@@ -1253,37 +1253,37 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
         <v>1.01</v>
@@ -1292,7 +1292,7 @@
         <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BD4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>7.4</v>
       </c>
       <c r="I5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1381,13 +1381,13 @@
         <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
         <v>2.56</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I6" t="n">
         <v>2.22</v>
@@ -1560,7 +1560,7 @@
         <v>1.58</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
         <v>1.58</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
         <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
         <v>3.8</v>
@@ -1745,152 +1745,152 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
         <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1939,152 +1939,152 @@
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
         <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H9" t="n">
         <v>3.75</v>
@@ -2127,158 +2127,158 @@
         <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K9" t="n">
         <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -2327,16 +2327,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
@@ -2345,134 +2345,134 @@
         <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -2503,34 +2503,34 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H11" t="n">
         <v>6.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>2.44</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
         <v>1.44</v>
@@ -2539,134 +2539,134 @@
         <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -2706,161 +2706,161 @@
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P12" t="n">
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>1.52</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="H13" t="n">
         <v>2.62</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="J13" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
         <v>3.3</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-21 18:20:22</t>
+          <t>2026-03-21 20:44:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -775,7 +775,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -907,7 +907,7 @@
         <v>9.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
         <v>10.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -1005,7 +1005,7 @@
         <v>1.19</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
         <v>6.4</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>1.97</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AX3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.6</v>
+        <v>1.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
         <v>3.1</v>
@@ -1154,49 +1154,49 @@
         <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,10 +1253,10 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR4" t="n">
         <v>16.5</v>
@@ -1265,7 +1265,7 @@
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
         <v>5.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.37</v>
@@ -1366,13 +1366,13 @@
         <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
         <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
@@ -1381,109 +1381,109 @@
         <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
         <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AP5" t="n">
         <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS5" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AT5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
         <v>14</v>
@@ -1492,17 +1492,17 @@
         <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -1533,55 +1533,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="W6" t="n">
         <v>1.2</v>
@@ -1593,7 +1593,7 @@
         <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BE6" t="n">
         <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
         <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
         <v>3.8</v>
@@ -1751,7 +1751,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
@@ -1766,13 +1766,13 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,10 +1835,10 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
         <v>14.5</v>
@@ -1847,7 +1847,7 @@
         <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
         <v>5.3</v>
@@ -1856,7 +1856,7 @@
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7" t="n">
         <v>12.5</v>
@@ -1871,10 +1871,10 @@
         <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1942,13 +1942,13 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
         <v>1.8</v>
@@ -1957,134 +1957,134 @@
         <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF8" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>34</v>
       </c>
-      <c r="AA8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX8" t="n">
         <v>13</v>
       </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF8" t="n">
         <v>17</v>
       </c>
-      <c r="AS8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.64</v>
-      </c>
       <c r="BG8" t="n">
-        <v>2.64</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>2.74</v>
@@ -2133,7 +2133,7 @@
         <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
@@ -2142,13 +2142,13 @@
         <v>2.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="P9" t="n">
         <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2166,16 +2166,16 @@
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y9" t="n">
         <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
         <v>130</v>
@@ -2184,7 +2184,7 @@
         <v>7.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
         <v>23</v>
@@ -2229,10 +2229,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
         <v>5.6</v>
@@ -2241,44 +2241,44 @@
         <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>20</v>
-      </c>
       <c r="BA9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB9" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB9" t="n">
-        <v>4</v>
-      </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.5</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.51</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="P11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
         <v>5.2</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,10 +2569,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2581,10 +2581,10 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AS11" t="n">
         <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>180</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>170</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>280</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG11" t="n">
         <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -2706,55 +2706,55 @@
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>1.49</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.52</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
         <v>1.56</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2805,46 +2805,46 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS12" t="n">
         <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
         <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
         <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BD12" t="n">
         <v>1.01</v>
@@ -2853,14 +2853,14 @@
         <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BG12" t="n">
         <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J13" t="n">
         <v>2.98</v>
@@ -2909,16 +2909,16 @@
         <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
         <v>1.55</v>
@@ -2927,134 +2927,134 @@
         <v>2.52</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -3103,16 +3103,16 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
         <v>1.07</v>
@@ -3121,134 +3121,134 @@
         <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H15" t="n">
-        <v>1.74</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.76</v>
+        <v>2.92</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-21 20:44:11</t>
+          <t>2026-03-21 23:06:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -787,13 +787,13 @@
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>4.1</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>6.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
@@ -972,40 +972,40 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
         <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W3" t="n">
         <v>1.19</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
         <v>6.4</v>
@@ -1014,7 +1014,7 @@
         <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
         <v>14.5</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.97</v>
+        <v>3.35</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AX3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>7.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H5" t="n">
         <v>7.2</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
         <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.37</v>
@@ -1372,7 +1372,7 @@
         <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
@@ -1387,10 +1387,10 @@
         <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
@@ -1453,10 +1453,10 @@
         <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>200</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
         <v>5.7</v>
@@ -1465,10 +1465,10 @@
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
         <v>7.2</v>
@@ -1480,7 +1480,7 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1489,10 +1489,10 @@
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>140</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>9.800000000000001</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
@@ -1560,7 +1560,7 @@
         <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P6" t="n">
         <v>1.57</v>
@@ -1572,7 +1572,7 @@
         <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
@@ -1581,10 +1581,10 @@
         <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1593,7 +1593,7 @@
         <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1641,52 +1641,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>75</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>100</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
@@ -1760,7 +1760,7 @@
         <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1769,7 +1769,7 @@
         <v>1.01</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
         <v>1.73</v>
@@ -1778,10 +1778,10 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1948,13 +1948,13 @@
         <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
         <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
@@ -1963,16 +1963,16 @@
         <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U8" t="n">
         <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
         <v>14.5</v>
@@ -1981,13 +1981,13 @@
         <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA8" t="n">
         <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
@@ -1999,19 +1999,19 @@
         <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
@@ -2038,7 +2038,7 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT8" t="n">
         <v>8.199999999999999</v>
@@ -2053,7 +2053,7 @@
         <v>36</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2062,36 +2062,36 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF8" t="n">
         <v>17</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.24</v>
+        <v>1.02</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
         <v>2.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
         <v>5.2</v>
@@ -2617,10 +2617,10 @@
         <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
         <v>4.1</v>
@@ -2629,22 +2629,22 @@
         <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>180</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>170</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -2653,10 +2653,10 @@
         <v>16.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>280</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>10.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -2706,10 +2706,10 @@
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
@@ -2736,7 +2736,7 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
@@ -2748,7 +2748,7 @@
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>26</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -2897,16 +2897,16 @@
         <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I13" t="n">
         <v>2.88</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2924,7 +2924,7 @@
         <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
@@ -2936,7 +2936,7 @@
         <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
         <v>1.53</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>
@@ -3300,13 +3300,13 @@
         <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
         <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
         <v>1.73</v>
@@ -3318,7 +3318,7 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,589 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-21 23:06:10</t>
+          <t>2026-03-22 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>90</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Olancho</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G18" t="n">
+        <v>880</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>980</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K18" t="n">
+        <v>950</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:27:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -763,16 +763,16 @@
         <v>3.85</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.48</v>
@@ -781,7 +781,7 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
@@ -805,7 +805,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
         <v>1.36</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -957,31 +957,31 @@
         <v>6.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="I3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
         <v>2.56</v>
@@ -993,13 +993,13 @@
         <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
         <v>1.19</v>
@@ -1044,10 +1044,10 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1059,22 +1059,22 @@
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.35</v>
+        <v>2.18</v>
       </c>
       <c r="AS3" t="n">
         <v>1.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AV3" t="n">
         <v>1.4</v>
@@ -1086,13 +1086,13 @@
         <v>1.23</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BB3" t="n">
         <v>1.15</v>
@@ -1104,17 +1104,17 @@
         <v>1.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF3" t="n">
         <v>1.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
         <v>7</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>180</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
         <v>170</v>
@@ -1435,7 +1435,7 @@
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
         <v>250</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1575,10 +1575,10 @@
         <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.88</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
@@ -1760,7 +1760,7 @@
         <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
         <v>2.44</v>
@@ -1936,7 +1936,7 @@
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1948,7 +1948,7 @@
         <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
         <v>1.8</v>
@@ -1963,7 +1963,7 @@
         <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
         <v>1.91</v>
@@ -1975,10 +1975,10 @@
         <v>1.7</v>
       </c>
       <c r="X8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
         <v>26</v>
@@ -2038,7 +2038,7 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>8.199999999999999</v>
@@ -2062,29 +2062,29 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
         <v>17</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -2318,10 +2318,10 @@
         <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
         <v>3.2</v>
@@ -2333,10 +2333,10 @@
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
         <v>1.41</v>
@@ -2348,19 +2348,19 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
         <v>7.4</v>
@@ -2402,7 +2402,7 @@
         <v>40</v>
       </c>
       <c r="AK10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="n">
         <v>85</v>
@@ -2417,16 +2417,16 @@
         <v>170</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>5.6</v>
@@ -2447,22 +2447,22 @@
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
         <v>4.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>8.4</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.75</v>
@@ -2524,7 +2524,7 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
         <v>2.58</v>
@@ -2545,13 +2545,13 @@
         <v>5.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
         <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
         <v>2.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="H12" t="n">
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
         <v>2.84</v>
@@ -2748,7 +2748,7 @@
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
         <v>3.4</v>
@@ -2900,25 +2900,25 @@
         <v>2.64</v>
       </c>
       <c r="I13" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
         <v>1.55</v>
@@ -2927,7 +2927,7 @@
         <v>2.56</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
         <v>5.1</v>
@@ -2939,7 +2939,7 @@
         <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W13" t="n">
         <v>1.42</v>
@@ -2954,13 +2954,13 @@
         <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
@@ -3008,7 +3008,7 @@
         <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3020,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX13" t="n">
         <v>17.5</v>
@@ -3032,29 +3032,29 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC13" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG13" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.94</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H15" t="n">
         <v>3.7</v>
@@ -3297,40 +3297,40 @@
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
         <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
         <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G16" t="n">
         <v>1.72</v>
@@ -3488,25 +3488,25 @@
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
         <v>1.27</v>
@@ -3518,7 +3518,7 @@
         <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
@@ -3623,7 +3623,7 @@
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
         <v>5.8</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -3667,31 +3667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
         <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O17" t="n">
         <v>1.69</v>
@@ -3709,7 +3709,7 @@
         <v>6.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="U17" t="n">
         <v>1.5</v>
@@ -3718,7 +3718,7 @@
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X17" t="n">
         <v>7.4</v>
@@ -3745,7 +3745,7 @@
         <v>210</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
         <v>15</v>
@@ -3757,7 +3757,7 @@
         <v>260</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK17" t="n">
         <v>34</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -799,10 +799,10 @@
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.68</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I3" t="n">
         <v>1.99</v>
@@ -975,13 +975,13 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
         <v>2.56</v>
@@ -990,10 +990,10 @@
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
         <v>1.72</v>
@@ -1002,7 +1002,7 @@
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
         <v>9</v>
@@ -1011,10 +1011,10 @@
         <v>6.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="n">
         <v>14.5</v>
@@ -1029,10 +1029,10 @@
         <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
@@ -1041,7 +1041,7 @@
         <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK3" t="n">
         <v>120</v>
@@ -1059,62 +1059,62 @@
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AU3" t="n">
         <v>4.8</v>
       </c>
       <c r="AV3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AW3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AW3" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AX3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.23</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG3" t="n">
         <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1339,70 +1339,70 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="AB5" t="n">
         <v>7</v>
@@ -1411,46 +1411,46 @@
         <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO5" t="n">
         <v>250</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>310</v>
       </c>
       <c r="AP5" t="n">
         <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1459,10 +1459,10 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>1.03</v>
@@ -1471,38 +1471,38 @@
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>170</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
         <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
@@ -1557,31 +1557,31 @@
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1590,7 +1590,7 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.03</v>
@@ -1656,7 +1656,7 @@
         <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
         <v>1.03</v>
@@ -1689,14 +1689,14 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
@@ -1760,13 +1760,13 @@
         <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
         <v>2.06</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
         <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
         <v>3.2</v>
@@ -2336,31 +2336,31 @@
         <v>2.24</v>
       </c>
       <c r="O10" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
         <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="T10" t="n">
         <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X10" t="n">
         <v>7.4</v>
@@ -2378,7 +2378,7 @@
         <v>7.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
         <v>23</v>
@@ -2417,16 +2417,16 @@
         <v>170</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
         <v>5.6</v>
@@ -2438,7 +2438,7 @@
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -2447,32 +2447,32 @@
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF10" t="n">
         <v>5</v>
       </c>
-      <c r="BF10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
         <v>8.4</v>
@@ -2527,7 +2527,7 @@
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
         <v>1.51</v>
@@ -2554,7 +2554,7 @@
         <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2617,10 +2617,10 @@
         <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT11" t="n">
         <v>4.1</v>
@@ -2629,10 +2629,10 @@
         <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -2641,10 +2641,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -2653,20 +2653,20 @@
         <v>16.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF11" t="n">
         <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>2.84</v>
@@ -2721,7 +2721,7 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
@@ -2730,13 +2730,13 @@
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
@@ -2748,7 +2748,7 @@
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.05</v>
       </c>
-      <c r="G13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.56</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.07</v>
+        <v>1.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,67 +3270,67 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.08</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>1.62</v>
       </c>
       <c r="G16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I16" t="n">
         <v>8.199999999999999</v>
@@ -3488,7 +3488,7 @@
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3497,16 +3497,16 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
         <v>1.27</v>
@@ -3524,7 +3524,7 @@
         <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X16" t="n">
         <v>16.5</v>
@@ -3551,7 +3551,7 @@
         <v>140</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -3584,13 +3584,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>5.4</v>
@@ -3599,10 +3599,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>7.2</v>
@@ -3614,7 +3614,7 @@
         <v>23</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
         <v>12.5</v>
@@ -3623,20 +3623,20 @@
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -3691,10 +3691,10 @@
         <v>1.16</v>
       </c>
       <c r="N17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
         <v>1.39</v>
@@ -3712,7 +3712,7 @@
         <v>2.64</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
@@ -3781,10 +3781,10 @@
         <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT17" t="n">
         <v>4.1</v>
@@ -3793,10 +3793,10 @@
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX17" t="n">
         <v>7.6</v>
@@ -3805,32 +3805,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB17" t="n">
         <v>15.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
       </c>
       <c r="BG17" t="n">
-        <v>90</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -775,7 +775,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -799,7 +799,7 @@
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
         <v>1.96</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="I3" t="n">
         <v>1.99</v>
@@ -966,7 +966,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
@@ -984,7 +984,7 @@
         <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -993,7 +993,7 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
         <v>1.72</v>
@@ -1002,7 +1002,7 @@
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
         <v>9</v>
@@ -1068,7 +1068,7 @@
         <v>1.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AT3" t="n">
         <v>1.56</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
         <v>1.09</v>
@@ -1196,7 +1196,7 @@
         <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G5" t="n">
         <v>1.72</v>
@@ -1351,7 +1351,7 @@
         <v>8.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1372,7 +1372,7 @@
         <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1390,7 +1390,7 @@
         <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1551,19 +1551,19 @@
         <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.4</v>
@@ -1590,7 +1590,7 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1647,7 +1647,7 @@
         <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
         <v>1.03</v>
@@ -1689,14 +1689,14 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BG6" t="n">
         <v>17.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
         <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
         <v>3.8</v>
@@ -1742,7 +1742,7 @@
         <v>2.58</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -1781,7 +1781,7 @@
         <v>1.43</v>
       </c>
       <c r="X7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1960,19 +1960,19 @@
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2008,7 +2008,7 @@
         <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
         <v>32</v>
@@ -2050,7 +2050,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>36</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
         <v>3.2</v>
@@ -2333,7 +2333,7 @@
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
         <v>1.64</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G11" t="n">
         <v>1.6</v>
@@ -2512,19 +2512,19 @@
         <v>8.4</v>
       </c>
       <c r="I11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
         <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
         <v>2.62</v>
@@ -2545,13 +2545,13 @@
         <v>5.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
         <v>2.66</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
         <v>3.15</v>
@@ -2721,7 +2721,7 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
@@ -2730,13 +2730,13 @@
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
@@ -2745,7 +2745,7 @@
         <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
         <v>1.56</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -2903,19 +2903,19 @@
         <v>5.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O13" t="n">
         <v>1.37</v>
@@ -2924,13 +2924,13 @@
         <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
         <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.86</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
         <v>2.56</v>
@@ -3130,7 +3130,7 @@
         <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
         <v>1.55</v>
@@ -3172,7 +3172,7 @@
         <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
         <v>75</v>
@@ -3181,7 +3181,7 @@
         <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3202,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT14" t="n">
         <v>8</v>
@@ -3238,17 +3238,17 @@
         <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
         <v>4.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.62</v>
       </c>
       <c r="G16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
         <v>6.4</v>
@@ -3491,7 +3491,7 @@
         <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -3506,7 +3506,7 @@
         <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
         <v>1.27</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v>980</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K18" t="n">
         <v>950</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -805,7 +805,7 @@
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W2" t="n">
         <v>1.36</v>
@@ -829,7 +829,7 @@
         <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -874,7 +874,7 @@
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -886,41 +886,41 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX2" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
         <v>19.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -951,43 +951,43 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G3" t="n">
         <v>5.6</v>
       </c>
       <c r="H3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.95</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.99</v>
-      </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
         <v>5.1</v>
@@ -996,16 +996,16 @@
         <v>2.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
         <v>1.22</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
         <v>6.4</v>
@@ -1020,7 +1020,7 @@
         <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
@@ -1038,7 +1038,7 @@
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
         <v>180</v>
@@ -1047,74 +1047,74 @@
         <v>120</v>
       </c>
       <c r="AL3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO3" t="n">
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.22</v>
+        <v>2.74</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="K4" t="n">
         <v>3.7</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.56</v>
       </c>
       <c r="G5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1372,7 +1372,7 @@
         <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1390,7 +1390,7 @@
         <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G6" t="n">
         <v>6.2</v>
@@ -1542,13 +1542,13 @@
         <v>1.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1581,7 +1581,7 @@
         <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1656,7 +1656,7 @@
         <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>1.03</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
         <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>1.02</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L10" t="n">
         <v>1.55</v>
@@ -2357,10 +2357,10 @@
         <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="X10" t="n">
         <v>7.4</v>
@@ -2372,10 +2372,10 @@
         <v>34</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC10" t="n">
         <v>7.6</v>
@@ -2387,10 +2387,10 @@
         <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
         <v>34</v>
@@ -2399,7 +2399,7 @@
         <v>140</v>
       </c>
       <c r="AJ10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
         <v>42</v>
@@ -2411,7 +2411,7 @@
         <v>320</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AO10" t="n">
         <v>170</v>
@@ -2423,13 +2423,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
@@ -2438,41 +2438,41 @@
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G11" t="n">
         <v>1.6</v>
@@ -2512,16 +2512,16 @@
         <v>8.4</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
         <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
@@ -2560,7 +2560,7 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2620,7 +2620,7 @@
         <v>4.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT11" t="n">
         <v>4.1</v>
@@ -2632,7 +2632,7 @@
         <v>4.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -2644,7 +2644,7 @@
         <v>4.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -2656,7 +2656,7 @@
         <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
         <v>10.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
@@ -2745,10 +2745,10 @@
         <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.37</v>
@@ -2924,13 +2924,13 @@
         <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
         <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
         <v>1.86</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.47</v>
@@ -3112,31 +3112,31 @@
         <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P14" t="n">
         <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V14" t="n">
         <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X14" t="n">
         <v>9</v>
@@ -3163,7 +3163,7 @@
         <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
         <v>17.5</v>
@@ -3214,7 +3214,7 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX14" t="n">
         <v>17.5</v>
@@ -3235,7 +3235,7 @@
         <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
         <v>4.9</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>6.4</v>
       </c>
       <c r="I16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -3503,10 +3503,10 @@
         <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
         <v>1.27</v>
@@ -3518,7 +3518,7 @@
         <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
@@ -3593,7 +3593,7 @@
         <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU16" t="n">
         <v>8.199999999999999</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H17" t="n">
         <v>6.2</v>
@@ -3691,7 +3691,7 @@
         <v>1.16</v>
       </c>
       <c r="N17" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.7</v>
@@ -3718,7 +3718,7 @@
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X17" t="n">
         <v>7.4</v>
@@ -3760,7 +3760,7 @@
         <v>25</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
         <v>110</v>
@@ -3769,7 +3769,7 @@
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
         <v>480</v>
@@ -3781,10 +3781,10 @@
         <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
         <v>4.1</v>
@@ -3793,10 +3793,10 @@
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
         <v>7.6</v>
@@ -3805,32 +3805,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
         <v>15.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>4.9</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H3" t="n">
         <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -975,7 +975,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.51</v>
@@ -999,7 +999,7 @@
         <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W3" t="n">
         <v>1.22</v>
@@ -1074,7 +1074,7 @@
         <v>2.34</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
         <v>2.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="I4" t="n">
         <v>4.1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.56</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
@@ -1357,7 +1357,7 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         <v>1.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
         <v>1.49</v>
@@ -1581,7 +1581,7 @@
         <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1590,7 +1590,7 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>2.58</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
@@ -1751,25 +1751,25 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
         <v>1.73</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -2357,10 +2357,10 @@
         <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X10" t="n">
         <v>7.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -2527,10 +2527,10 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
         <v>1.53</v>
@@ -2569,23 +2569,23 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG11" t="n">
         <v>12</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH11" t="n">
         <v>1000</v>
       </c>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS11" t="n">
         <v>7</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AT11" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>50</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
         <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="H12" t="n">
         <v>3.15</v>
@@ -2709,7 +2709,7 @@
         <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
@@ -2721,7 +2721,7 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
@@ -2730,7 +2730,7 @@
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -2748,7 +2748,7 @@
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="G13" t="n">
         <v>2.04</v>
@@ -2900,46 +2900,46 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U13" t="n">
         <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
         <v>1.96</v>
@@ -3047,14 +3047,14 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG13" t="n">
         <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -3142,34 +3142,34 @@
         <v>9</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG14" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>75</v>
@@ -3187,7 +3187,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO14" t="n">
         <v>55</v>
@@ -3202,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT14" t="n">
         <v>8</v>
@@ -3214,7 +3214,7 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
         <v>17.5</v>
@@ -3226,36 +3226,36 @@
         <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.08</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,378 +3653,572 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="G17" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="P17" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
         <v>6.8</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>320</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
         <v>32</v>
       </c>
       <c r="AE17" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AF17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG17" t="n">
-        <v>15</v>
-      </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS17" t="n">
         <v>6</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7</v>
-      </c>
       <c r="AT17" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA17" t="n">
         <v>6</v>
       </c>
-      <c r="BA17" t="n">
-        <v>7</v>
-      </c>
       <c r="BB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC17" t="n">
         <v>15.5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-22 13:04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Lobos UPNFM</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Olancho</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>1.04</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>880</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>1.04</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>980</v>
       </c>
-      <c r="J18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K19" t="n">
         <v>950</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
         <v>1.25</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>1.25</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>1.25</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1.18</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>1.25</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-03-22 10:49:47</t>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,7 +763,7 @@
         <v>3.85</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
         <v>2.46</v>
@@ -772,7 +772,7 @@
         <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.48</v>
@@ -787,13 +787,13 @@
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>4.1</v>
@@ -805,10 +805,10 @@
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
         <v>12</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>5.5</v>
@@ -960,55 +960,55 @@
         <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
         <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W3" t="n">
         <v>1.22</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z3" t="n">
         <v>10.5</v>
@@ -1029,7 +1029,7 @@
         <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
         <v>23</v>
@@ -1038,83 +1038,83 @@
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AK3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL3" t="n">
         <v>120</v>
       </c>
-      <c r="AL3" t="n">
-        <v>130</v>
-      </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.62</v>
+        <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.99</v>
+        <v>2.72</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.66</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.74</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
@@ -1330,179 +1330,179 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK5" t="n">
         <v>21</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AL5" t="n">
         <v>65</v>
       </c>
-      <c r="AA5" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>60</v>
-      </c>
       <c r="AM5" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU5" t="n">
         <v>9</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>150</v>
       </c>
       <c r="BB5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>12</v>
       </c>
-      <c r="BC5" t="n">
-        <v>15</v>
-      </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
@@ -1524,139 +1524,139 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
+        <v>1.57</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>1.69</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="I6" t="n">
-        <v>2.08</v>
+        <v>8.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB6" t="n">
         <v>7</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>1.03</v>
@@ -1665,45 +1665,45 @@
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
         <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,78 +1713,78 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="I7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.85</v>
       </c>
-      <c r="J7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.56</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.47</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1835,13 +1835,13 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS7" t="n">
         <v>1.03</v>
@@ -1850,7 +1850,7 @@
         <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
         <v>1.03</v>
@@ -1883,21 +1883,21 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,117 +1907,117 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2026,72 +2026,72 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,117 +2101,117 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2220,72 +2220,72 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>1.75</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD11" t="n">
         <v>23</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>16</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AW11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD11" t="n">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,86 +2688,86 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.24</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>1.58</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
         <v>4.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="O12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.53</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.49</v>
-      </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>2.72</v>
       </c>
       <c r="X12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC12" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD12" t="n">
         <v>1000</v>
       </c>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF12" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
@@ -2877,78 +2877,78 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,10 +2957,10 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -3047,21 +3047,21 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BG13" t="n">
         <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.43</v>
+        <v>1.96</v>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BG14" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP15" t="n">
         <v>7.8</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AQ15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR15" t="n">
         <v>14</v>
       </c>
-      <c r="Y15" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.08</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,378 +3847,572 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
         <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.16</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.17</v>
-      </c>
       <c r="W18" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA18" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
         <v>32</v>
       </c>
       <c r="AE18" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="AF18" t="n">
         <v>10.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>480</v>
+        <v>190</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AR18" t="n">
         <v>6.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE18" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE18" t="n">
-        <v>7</v>
-      </c>
       <c r="BF18" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-22 15:15:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Lobos UPNFM</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Olancho</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>1.04</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>880</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>1.04</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>980</v>
       </c>
-      <c r="J19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="J20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K20" t="n">
         <v>950</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
         <v>1.25</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O20" t="n">
         <v>1.25</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P20" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q20" t="n">
         <v>1.25</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>1.18</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
         <v>1.25</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-22 13:04:15</t>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H2" t="n">
         <v>2.3</v>
@@ -769,13 +769,13 @@
         <v>2.46</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -805,7 +805,7 @@
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W2" t="n">
         <v>1.35</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J3" t="n">
         <v>3.5</v>
@@ -1026,7 +1026,7 @@
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
         <v>38</v>
@@ -1035,7 +1035,7 @@
         <v>23</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
@@ -1062,22 +1062,22 @@
         <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR3" t="n">
         <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="AT3" t="n">
         <v>5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
         <v>2.16</v>
@@ -1086,19 +1086,19 @@
         <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7</v>
       </c>
       <c r="BD3" t="n">
         <v>7.2</v>
@@ -1107,14 +1107,14 @@
         <v>2.14</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="BG3" t="n">
         <v>16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="H4" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q4" t="n">
         <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
         <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
@@ -1339,67 +1339,67 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G5" t="n">
         <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1408,10 +1408,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1432,77 +1432,77 @@
         <v>13</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>85</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU5" t="n">
         <v>9</v>
       </c>
       <c r="AV5" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>26</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>150</v>
+        <v>4.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
         <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4.4</v>
@@ -1560,13 +1560,13 @@
         <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
         <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R6" t="n">
         <v>1.26</v>
@@ -1575,7 +1575,7 @@
         <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.73</v>
@@ -1584,7 +1584,7 @@
         <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
         <v>14</v>
@@ -1596,7 +1596,7 @@
         <v>65</v>
       </c>
       <c r="AA6" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="AB6" t="n">
         <v>7</v>
@@ -1605,7 +1605,7 @@
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
         <v>160</v>
@@ -1623,13 +1623,13 @@
         <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>240</v>
@@ -1638,7 +1638,7 @@
         <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AP6" t="n">
         <v>9</v>
@@ -1656,7 +1656,7 @@
         <v>5.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>1.03</v>
@@ -1692,11 +1692,11 @@
         <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>90</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -1751,7 +1751,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
         <v>1.49</v>
@@ -1760,7 +1760,7 @@
         <v>1.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
@@ -1772,7 +1772,7 @@
         <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
         <v>1.92</v>
@@ -1835,69 +1835,69 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
         <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BF7" t="n">
-        <v>100</v>
+        <v>1.91</v>
       </c>
       <c r="BG7" t="n">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.46</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>1.42</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>5.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.11</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>3.35</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,117 +2101,117 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2220,72 +2220,72 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,117 +2295,117 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2414,72 +2414,72 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="O11" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>1.58</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>2.72</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD12" t="n">
         <v>23</v>
       </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
         <v>16</v>
       </c>
-      <c r="AR12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>6</v>
-      </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
         <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,86 +2882,86 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.24</v>
+        <v>1.52</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>1.57</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>2.72</v>
       </c>
       <c r="X13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC13" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD13" t="n">
         <v>1000</v>
       </c>
@@ -2969,10 +2969,10 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
@@ -3071,78 +3071,78 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04</v>
+        <v>2.68</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3193,10 +3193,10 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
         <v>1.03</v>
@@ -3205,22 +3205,22 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.03</v>
@@ -3241,21 +3241,21 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.05</v>
       </c>
-      <c r="G15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.72</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.64</v>
+        <v>1.96</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
       <c r="X15" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG15" t="n">
         <v>60</v>
       </c>
-      <c r="AL15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>6</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="I16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT16" t="n">
         <v>8</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R17" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
         <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.08</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="T18" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,378 +4041,572 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
         <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.2</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.16</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="W19" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
         <v>32</v>
       </c>
       <c r="AE19" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="AF19" t="n">
         <v>10.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AI19" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>480</v>
+        <v>190</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AR19" t="n">
         <v>6.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE19" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE19" t="n">
-        <v>7</v>
-      </c>
       <c r="BF19" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>490</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Lobos UPNFM</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Olancho</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>1.04</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>880</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>1.04</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>980</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1.04</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>950</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
         <v>1.25</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>1.25</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>1.25</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1.18</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>1.25</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-03-22 15:15:12</t>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -775,7 +775,7 @@
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -793,7 +793,7 @@
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>4.1</v>
@@ -802,13 +802,13 @@
         <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
         <v>1.69</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
         <v>12</v>
@@ -817,10 +817,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
@@ -832,19 +832,19 @@
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG2" t="n">
         <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -853,13 +853,13 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -886,41 +886,41 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10</v>
       </c>
       <c r="BG2" t="n">
         <v>19.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -978,7 +978,7 @@
         <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
         <v>1.62</v>
@@ -1011,110 +1011,110 @@
         <v>7.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.5</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
         <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO3" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.72</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.16</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
         <v>29</v>
       </c>
       <c r="AY3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>5.8</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.14</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>5.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1193,13 +1193,13 @@
         <v>1.79</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1214,7 +1214,7 @@
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AV4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA4" t="n">
         <v>3.75</v>
       </c>
-      <c r="AW4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="BB4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD4" t="n">
         <v>3.6</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BE4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF4" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1366,7 +1366,7 @@
         <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
         <v>1.95</v>
@@ -1381,7 +1381,7 @@
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
         <v>1.65</v>
@@ -1390,16 +1390,16 @@
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1408,10 +1408,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1420,22 +1420,22 @@
         <v>8.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1447,10 +1447,10 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
         <v>4.5</v>
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW5" t="n">
         <v>4.6</v>
@@ -1477,7 +1477,7 @@
         <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BA5" t="n">
         <v>4.6</v>
@@ -1486,10 +1486,10 @@
         <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
         <v>4.6</v>
@@ -1498,11 +1498,11 @@
         <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>1.66</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I6" t="n">
         <v>8.6</v>
@@ -1575,10 +1575,10 @@
         <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -1593,7 +1593,7 @@
         <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AA6" t="n">
         <v>350</v>
@@ -1626,16 +1626,16 @@
         <v>18.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO6" t="n">
         <v>310</v>
@@ -1647,22 +1647,22 @@
         <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
         <v>6.6</v>
@@ -1674,7 +1674,7 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1686,17 +1686,17 @@
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
         <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>90</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1730,64 +1730,64 @@
         <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
         <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -1796,10 +1796,10 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
         <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.16</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF7" t="n">
         <v>2.18</v>
       </c>
-      <c r="BB7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
         <v>5.9</v>
@@ -1942,10 +1942,10 @@
         <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
@@ -1957,88 +1957,88 @@
         <v>1.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>540</v>
       </c>
       <c r="AA8" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF8" t="n">
         <v>11</v>
       </c>
-      <c r="AC8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AK8" t="n">
         <v>14.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS8" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>12</v>
       </c>
       <c r="AT8" t="n">
         <v>9.199999999999999</v>
@@ -2047,44 +2047,44 @@
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
         <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2124,19 +2124,19 @@
         <v>2.96</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J9" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
         <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
         <v>2.4</v>
@@ -2145,10 +2145,10 @@
         <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2163,7 +2163,7 @@
         <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
         <v>1.43</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2312,34 +2312,34 @@
         <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
         <v>2.12</v>
@@ -2351,13 +2351,13 @@
         <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
         <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
         <v>1.71</v>
@@ -2369,13 +2369,13 @@
         <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
@@ -2390,16 +2390,16 @@
         <v>16.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="n">
         <v>32</v>
@@ -2408,10 +2408,10 @@
         <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO10" t="n">
         <v>55</v>
@@ -2426,10 +2426,10 @@
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
@@ -2438,41 +2438,41 @@
         <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BF10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG10" t="n">
         <v>42</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,10 +2569,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2584,7 +2584,7 @@
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2596,7 +2596,7 @@
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
         <v>4.2</v>
@@ -2709,34 +2709,34 @@
         <v>4.9</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.28</v>
@@ -2745,7 +2745,7 @@
         <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.74</v>
@@ -2754,13 +2754,13 @@
         <v>7.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
         <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB12" t="n">
         <v>6.6</v>
@@ -2784,22 +2784,22 @@
         <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="n">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AM12" t="n">
         <v>320</v>
       </c>
       <c r="AN12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AO12" t="n">
         <v>170</v>
@@ -2808,25 +2808,25 @@
         <v>6.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2835,16 +2835,16 @@
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BD12" t="n">
         <v>7.2</v>
@@ -2853,14 +2853,14 @@
         <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
         <v>7.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
@@ -2912,16 +2912,16 @@
         <v>1.61</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
         <v>2.54</v>
@@ -2936,19 +2936,19 @@
         <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W13" t="n">
         <v>2.72</v>
       </c>
       <c r="X13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2963,7 +2963,7 @@
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -2972,7 +2972,7 @@
         <v>7.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
@@ -2984,7 +2984,7 @@
         <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,22 +3005,22 @@
         <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU13" t="n">
         <v>8.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="n">
         <v>6.2</v>
@@ -3029,32 +3029,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
         <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD13" t="n">
         <v>50</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -3094,16 +3094,16 @@
         <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
@@ -3112,13 +3112,13 @@
         <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
         <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
@@ -3136,46 +3136,46 @@
         <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X14" t="n">
         <v>10.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3199,10 +3199,10 @@
         <v>7.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
         <v>5.5</v>
@@ -3214,41 +3214,41 @@
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>65</v>
+        <v>5.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         <v>1.98</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
         <v>1000</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG15" t="n">
         <v>1000</v>
@@ -3381,68 +3381,68 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY15" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>60</v>
+        <v>4.7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>3.35</v>
       </c>
       <c r="H16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
         <v>2.8</v>
@@ -3488,13 +3488,13 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N16" t="n">
         <v>2.72</v>
@@ -3602,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>17.5</v>
@@ -3617,7 +3617,7 @@
         <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
         <v>40</v>
@@ -3626,17 +3626,17 @@
         <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
         <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
         <v>5.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -3721,116 +3721,116 @@
         <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
         <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>100</v>
+        <v>470</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
         <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>370</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
         <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>130</v>
+        <v>320</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
         <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -4085,7 +4085,7 @@
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
         <v>2.06</v>
@@ -4094,40 +4094,40 @@
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
         <v>130</v>
@@ -4139,7 +4139,7 @@
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>130</v>
@@ -4160,19 +4160,19 @@
         <v>13.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP19" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="AR19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS19" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
         <v>5.8</v>
@@ -4181,44 +4181,44 @@
         <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
         <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
         <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H20" t="n">
         <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
         <v>1.55</v>
@@ -4276,7 +4276,7 @@
         <v>2.26</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P20" t="n">
         <v>1.41</v>
@@ -4297,13 +4297,13 @@
         <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y20" t="n">
         <v>14.5</v>
@@ -4312,7 +4312,7 @@
         <v>55</v>
       </c>
       <c r="AA20" t="n">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="AB20" t="n">
         <v>5.4</v>
@@ -4330,7 +4330,7 @@
         <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
         <v>40</v>
@@ -4348,13 +4348,13 @@
         <v>110</v>
       </c>
       <c r="AM20" t="n">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="AN20" t="n">
         <v>28</v>
       </c>
       <c r="AO20" t="n">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="AP20" t="n">
         <v>6</v>
@@ -4363,10 +4363,10 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
         <v>4.7</v>
@@ -4375,10 +4375,10 @@
         <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX20" t="n">
         <v>7.6</v>
@@ -4387,32 +4387,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>880</v>
+        <v>970</v>
       </c>
       <c r="H21" t="n">
         <v>1.04</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -760,16 +760,16 @@
         <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
         <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
@@ -781,40 +781,40 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
         <v>1.69</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z2" t="n">
         <v>24</v>
@@ -823,10 +823,10 @@
         <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
         <v>11.5</v>
@@ -835,7 +835,7 @@
         <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="n">
         <v>15.5</v>
@@ -847,10 +847,10 @@
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AL2" t="n">
         <v>65</v>
@@ -859,7 +859,7 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
@@ -901,26 +901,26 @@
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
         <v>19.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
         <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
@@ -1002,7 +1002,7 @@
         <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
@@ -1017,19 +1017,19 @@
         <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
         <v>500</v>
@@ -1059,7 +1059,7 @@
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>6</v>
@@ -1068,53 +1068,53 @@
         <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
         <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
         <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
@@ -1187,7 +1187,7 @@
         <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
         <v>1.79</v>
@@ -1235,7 +1235,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AW4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB4" t="n">
         <v>3.6</v>
       </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1363,10 +1363,10 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>1.95</v>
@@ -1381,7 +1381,7 @@
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
         <v>1.65</v>
@@ -1432,7 +1432,7 @@
         <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1486,7 +1486,7 @@
         <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
         <v>4.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G6" t="n">
         <v>1.66</v>
@@ -1548,37 +1548,37 @@
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
         <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -1590,22 +1590,22 @@
         <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
         <v>160</v>
       </c>
       <c r="AA6" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AB6" t="n">
         <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
         <v>160</v>
@@ -1614,31 +1614,31 @@
         <v>10.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
         <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AP6" t="n">
         <v>9</v>
@@ -1647,25 +1647,25 @@
         <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY6" t="n">
         <v>7.6</v>
@@ -1674,7 +1674,7 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1683,20 +1683,20 @@
         <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
         <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
         <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.88</v>
@@ -1775,7 +1775,7 @@
         <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.23</v>
@@ -1844,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -1856,41 +1856,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="BE7" t="n">
         <v>3.35</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BG7" t="n">
         <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1921,136 +1921,136 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
         <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
         <v>1.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="AA8" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AE8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="AR8" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW8" t="n">
         <v>10</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2059,22 +2059,22 @@
         <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
         <v>4.6</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2178,7 +2178,7 @@
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>1000</v>
@@ -2232,7 +2232,7 @@
         <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
@@ -2244,7 +2244,7 @@
         <v>4.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AX9" t="n">
         <v>5.1</v>
@@ -2253,32 +2253,32 @@
         <v>4.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BD9" t="n">
         <v>2.46</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
         <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
         <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2351,16 +2351,16 @@
         <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
         <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
@@ -2399,7 +2399,7 @@
         <v>130</v>
       </c>
       <c r="AJ10" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
         <v>32</v>
@@ -2408,10 +2408,10 @@
         <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
         <v>55</v>
@@ -2438,7 +2438,7 @@
         <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2450,10 +2450,10 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
         <v>2.38</v>
@@ -2542,10 +2542,10 @@
         <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U11" t="n">
         <v>1.92</v>
@@ -2554,13 +2554,13 @@
         <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2575,7 +2575,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
@@ -2629,10 +2629,10 @@
         <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX11" t="n">
         <v>10</v>
@@ -2644,29 +2644,29 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF11" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
         <v>4.2</v>
@@ -2715,7 +2715,7 @@
         <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
         <v>1.15</v>
@@ -2730,7 +2730,7 @@
         <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
         <v>1.16</v>
@@ -2739,13 +2739,13 @@
         <v>6.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
         <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
         <v>1.74</v>
@@ -2754,7 +2754,7 @@
         <v>7.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
         <v>34</v>
@@ -2781,13 +2781,13 @@
         <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
         <v>540</v>
       </c>
       <c r="AJ12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
         <v>38</v>
@@ -2796,16 +2796,16 @@
         <v>460</v>
       </c>
       <c r="AM12" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO12" t="n">
         <v>170</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>9</v>
@@ -2838,7 +2838,7 @@
         <v>23</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -2847,20 +2847,20 @@
         <v>29</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
         <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.61</v>
@@ -2915,146 +2915,146 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.68</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V13" t="n">
         <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>60</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>15</v>
       </c>
-      <c r="AK13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>16</v>
-      </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AT13" t="n">
         <v>4.9</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW13" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BB13" t="n">
         <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>2.26</v>
       </c>
       <c r="G14" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H14" t="n">
         <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
         <v>2.72</v>
@@ -3106,19 +3106,19 @@
         <v>1.54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O14" t="n">
         <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
@@ -3127,10 +3127,10 @@
         <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
         <v>1.3</v>
@@ -3151,31 +3151,31 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG14" t="n">
         <v>34</v>
       </c>
-      <c r="AG14" t="n">
-        <v>25</v>
-      </c>
       <c r="AH14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3202,19 +3202,19 @@
         <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -3226,29 +3226,29 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
         <v>13</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
         <v>2.02</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
         <v>5.7</v>
@@ -3324,7 +3324,7 @@
         <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V15" t="n">
         <v>1.21</v>
@@ -3333,7 +3333,7 @@
         <v>1.98</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
         <v>1000</v>
@@ -3348,7 +3348,7 @@
         <v>27</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3369,7 +3369,7 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
         <v>1000</v>
@@ -3390,13 +3390,13 @@
         <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="AT15" t="n">
         <v>4.4</v>
@@ -3405,44 +3405,44 @@
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY15" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="BB15" t="n">
         <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.2</v>
+        <v>3.15</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3476,37 +3476,37 @@
         <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L16" t="n">
         <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
         <v>1.52</v>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
         <v>1.2</v>
@@ -3518,13 +3518,13 @@
         <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V16" t="n">
         <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>9</v>
@@ -3563,7 +3563,7 @@
         <v>75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
         <v>60</v>
@@ -3575,7 +3575,7 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
         <v>55</v>
@@ -3590,10 +3590,10 @@
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.4</v>
@@ -3614,29 +3614,29 @@
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB16" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
         <v>40</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
         <v>6.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -3691,10 +3691,10 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
         <v>1.78</v>
@@ -3706,22 +3706,22 @@
         <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
         <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
         <v>16.5</v>
@@ -3733,7 +3733,7 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC17" t="n">
         <v>8.6</v>
@@ -3751,10 +3751,10 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="AJ17" t="n">
         <v>21</v>
@@ -3766,25 +3766,25 @@
         <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AP17" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
         <v>4.9</v>
@@ -3793,10 +3793,10 @@
         <v>4.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX17" t="n">
         <v>5.6</v>
@@ -3805,32 +3805,32 @@
         <v>7</v>
       </c>
       <c r="AZ17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB17" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BC17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3861,91 +3861,91 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P18" t="n">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3954,7 +3954,7 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
         <v>6.2</v>
@@ -4067,7 +4067,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
@@ -4085,7 +4085,7 @@
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
         <v>2.06</v>
@@ -4100,7 +4100,7 @@
         <v>1.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
         <v>1.17</v>
@@ -4142,7 +4142,7 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -4166,7 +4166,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
         <v>40</v>
@@ -4175,13 +4175,13 @@
         <v>6.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
         <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>22</v>
+        <v>5.4</v>
       </c>
       <c r="AW19" t="n">
         <v>6.2</v>
@@ -4190,13 +4190,13 @@
         <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
         <v>12.5</v>
@@ -4205,7 +4205,7 @@
         <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE19" t="n">
         <v>6.2</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="T20" t="n">
         <v>2.64</v>
@@ -4318,25 +4318,25 @@
         <v>5.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>32</v>
       </c>
       <c r="AE20" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AF20" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>40</v>
       </c>
       <c r="AI20" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AJ20" t="n">
         <v>22</v>
@@ -4360,13 +4360,13 @@
         <v>6</v>
       </c>
       <c r="AQ20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS20" t="n">
         <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
         <v>4.7</v>
@@ -4375,10 +4375,10 @@
         <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>7.6</v>
@@ -4387,32 +4387,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
         <v>19.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H2" t="n">
         <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -775,7 +775,7 @@
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -799,16 +799,16 @@
         <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -817,28 +817,28 @@
         <v>8.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
         <v>60</v>
@@ -847,10 +847,10 @@
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>65</v>
@@ -859,13 +859,13 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
         <v>7.6</v>
@@ -874,7 +874,7 @@
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -892,35 +892,35 @@
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BE2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -951,76 +951,76 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.23</v>
       </c>
-      <c r="S3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
@@ -1056,7 +1056,7 @@
         <v>700</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
         <v>6.8</v>
@@ -1065,56 +1065,56 @@
         <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>2.44</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.4</v>
+        <v>2.98</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.2</v>
+        <v>2.52</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>2.52</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1154,19 +1154,19 @@
         <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
         <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
         <v>2.6</v>
@@ -1178,7 +1178,7 @@
         <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
@@ -1190,13 +1190,13 @@
         <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
@@ -1214,7 +1214,7 @@
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.6</v>
+        <v>2.02</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.55</v>
+        <v>2.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.65</v>
+        <v>1.93</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H5" t="n">
         <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
         <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1381,19 +1381,19 @@
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
         <v>3.5</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>80</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>120</v>
@@ -1417,10 +1417,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.6</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="AH5" t="n">
         <v>95</v>
@@ -1429,10 +1429,10 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT5" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AU5" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8</v>
-      </c>
       <c r="BC5" t="n">
-        <v>12</v>
+        <v>2.94</v>
       </c>
       <c r="BD5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.4</v>
       </c>
-      <c r="BE5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G6" t="n">
         <v>1.66</v>
@@ -1542,7 +1542,7 @@
         <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
@@ -1560,58 +1560,58 @@
         <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
         <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
         <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
         <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
         <v>340</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1641,62 +1641,62 @@
         <v>290</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
         <v>5.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>7.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
@@ -1748,34 +1748,34 @@
         <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
         <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W7" t="n">
         <v>1.23</v>
@@ -1787,16 +1787,16 @@
         <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>36</v>
@@ -1811,7 +1811,7 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BF7" t="n">
         <v>2.22</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.39</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.41</v>
       </c>
       <c r="H8" t="n">
         <v>9.4</v>
@@ -1933,10 +1933,10 @@
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.25</v>
@@ -1951,7 +1951,7 @@
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
         <v>1.58</v>
@@ -1960,19 +1960,19 @@
         <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
         <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="X8" t="n">
         <v>27</v>
@@ -1984,13 +1984,13 @@
         <v>90</v>
       </c>
       <c r="AA8" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
         <v>36</v>
@@ -1999,7 +1999,7 @@
         <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
@@ -2011,7 +2011,7 @@
         <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>13.5</v>
@@ -2020,25 +2020,25 @@
         <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
         <v>34</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
         <v>9.4</v>
@@ -2050,28 +2050,28 @@
         <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
         <v>28</v>
@@ -2080,11 +2080,11 @@
         <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
         <v>2.96</v>
       </c>
       <c r="I9" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
         <v>2.72</v>
@@ -2136,16 +2136,16 @@
         <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
         <v>2.68</v>
@@ -2154,22 +2154,22 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>4.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
@@ -2241,44 +2241,44 @@
         <v>4.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.4</v>
+        <v>2.28</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>2.74</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
         <v>2.36</v>
@@ -2327,7 +2327,7 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2339,13 +2339,13 @@
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
         <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
         <v>3.9</v>
@@ -2357,55 +2357,55 @@
         <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
         <v>1.73</v>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
         <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2414,65 +2414,65 @@
         <v>24</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
         <v>4.2</v>
@@ -2521,7 +2521,7 @@
         <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2533,10 +2533,10 @@
         <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
         <v>1.26</v>
@@ -2545,16 +2545,16 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -2566,16 +2566,16 @@
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
@@ -2584,7 +2584,7 @@
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU11" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="AV11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY11" t="n">
         <v>5.4</v>
       </c>
-      <c r="AT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>5.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.3</v>
+        <v>2.78</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.7</v>
+        <v>2.84</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R12" t="n">
         <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
         <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
         <v>6.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AF12" t="n">
         <v>12.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
         <v>540</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>460</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="n">
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO12" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR12" t="n">
         <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
         <v>17.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY12" t="n">
         <v>10</v>
       </c>
-      <c r="AY12" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G13" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
         <v>9.199999999999999</v>
@@ -2915,7 +2915,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
         <v>1.57</v>
@@ -2927,28 +2927,28 @@
         <v>2.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
         <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z13" t="n">
         <v>170</v>
@@ -2957,10 +2957,10 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
         <v>80</v>
@@ -2972,89 +2972,89 @@
         <v>7.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS13" t="n">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AW13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX13" t="n">
         <v>6.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="BB13" t="n">
         <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="BF13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G14" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
         <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
@@ -3118,7 +3118,7 @@
         <v>1.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
@@ -3133,37 +3133,37 @@
         <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
         <v>34</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3193,16 +3193,16 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
@@ -3211,44 +3211,44 @@
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.2</v>
+        <v>2.98</v>
       </c>
       <c r="BB14" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -3303,7 +3303,7 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>1.36</v>
@@ -3312,25 +3312,25 @@
         <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
         <v>1.89</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X15" t="n">
         <v>90</v>
@@ -3390,59 +3390,59 @@
         <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AT15" t="n">
         <v>4.4</v>
       </c>
       <c r="AU15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BB15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>9</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="BE15" t="n">
         <v>3.15</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
         <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
@@ -3500,7 +3500,7 @@
         <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P16" t="n">
         <v>1.58</v>
@@ -3512,7 +3512,7 @@
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T16" t="n">
         <v>2.08</v>
@@ -3527,49 +3527,49 @@
         <v>1.44</v>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB16" t="n">
         <v>9.6</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
         <v>7.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>23</v>
       </c>
-      <c r="AG16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>26</v>
-      </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3578,22 +3578,22 @@
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>6.4</v>
@@ -3602,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AX16" t="n">
         <v>17.5</v>
@@ -3614,29 +3614,29 @@
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G17" t="n">
         <v>1.92</v>
@@ -3679,7 +3679,7 @@
         <v>5.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -3691,25 +3691,25 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
         <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
         <v>1.87</v>
@@ -3727,7 +3727,7 @@
         <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
@@ -3742,7 +3742,7 @@
         <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="AF17" t="n">
         <v>11</v>
@@ -3751,10 +3751,10 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AI17" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AJ17" t="n">
         <v>21</v>
@@ -3763,7 +3763,7 @@
         <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
@@ -3775,62 +3775,62 @@
         <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB17" t="n">
         <v>9</v>
       </c>
-      <c r="AX17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA17" t="n">
+      <c r="BC17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BE17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3864,37 +3864,37 @@
         <v>2.94</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H18" t="n">
         <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
         <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
         <v>1.19</v>
@@ -3909,16 +3909,16 @@
         <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z18" t="n">
         <v>20</v>
@@ -3927,34 +3927,34 @@
         <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE18" t="n">
         <v>50</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
         <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO18" t="n">
         <v>60</v>
@@ -3972,59 +3972,59 @@
         <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
         <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -4085,10 +4085,10 @@
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
@@ -4103,25 +4103,25 @@
         <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC19" t="n">
         <v>9.800000000000001</v>
@@ -4136,7 +4136,7 @@
         <v>10.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -4145,13 +4145,13 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4166,22 +4166,22 @@
         <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>6.2</v>
@@ -4190,35 +4190,35 @@
         <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
         <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE19" t="n">
         <v>6.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
         <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>1.81</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H20" t="n">
         <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J20" t="n">
         <v>3.2</v>
@@ -4273,61 +4273,61 @@
         <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O20" t="n">
         <v>1.71</v>
       </c>
       <c r="P20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q20" t="n">
         <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X20" t="n">
         <v>7.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AA20" t="n">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
         <v>32</v>
       </c>
       <c r="AE20" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
@@ -4339,80 +4339,80 @@
         <v>270</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>520</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>530</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>32</v>
       </c>
-      <c r="AL20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>530</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>560</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BA20" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
         <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -775,49 +775,49 @@
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA2" t="n">
         <v>120</v>
@@ -838,7 +838,7 @@
         <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AH2" t="n">
         <v>60</v>
@@ -847,7 +847,7 @@
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
@@ -859,7 +859,7 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AO2" t="n">
         <v>46</v>
@@ -892,35 +892,35 @@
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>50</v>
       </c>
       <c r="BE2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF2" t="n">
         <v>12.5</v>
       </c>
-      <c r="BF2" t="n">
-        <v>11</v>
-      </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
         <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
         <v>970</v>
@@ -1017,10 +1017,10 @@
         <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
@@ -1062,59 +1062,59 @@
         <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>5.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE3" t="n">
         <v>11</v>
       </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="O4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
@@ -1256,59 +1256,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G5" t="n">
         <v>1.39</v>
@@ -1348,52 +1348,52 @@
         <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
         <v>80</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
         <v>42</v>
@@ -1420,7 +1420,7 @@
         <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>95</v>
@@ -1429,10 +1429,10 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1450,7 +1450,7 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR5" t="n">
         <v>4.2</v>
@@ -1477,7 +1477,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1486,23 +1486,23 @@
         <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1533,70 +1533,70 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="H6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
         <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.76</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA6" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AB6" t="n">
         <v>7.2</v>
@@ -1608,7 +1608,7 @@
         <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
@@ -1617,25 +1617,25 @@
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
         <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
         <v>19.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
         <v>290</v>
@@ -1647,13 +1647,13 @@
         <v>17.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
@@ -1662,7 +1662,7 @@
         <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>7.4</v>
@@ -1671,32 +1671,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>15.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
         <v>2.08</v>
@@ -1775,13 +1775,13 @@
         <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>16.5</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="n">
         <v>36</v>
@@ -1811,7 +1811,7 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -1844,53 +1844,53 @@
         <v>5.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV7" t="n">
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BG7" t="n">
         <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="n">
         <v>9.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
         <v>5.6</v>
       </c>
       <c r="K8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N8" t="n">
         <v>5.9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
@@ -1960,31 +1960,31 @@
         <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
         <v>3.5</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
         <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
@@ -1993,7 +1993,7 @@
         <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
         <v>130</v>
@@ -2002,13 +2002,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="AJ8" t="n">
         <v>12</v>
@@ -2029,19 +2029,19 @@
         <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
         <v>34</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
         <v>11.5</v>
@@ -2050,10 +2050,10 @@
         <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>9.4</v>
@@ -2062,29 +2062,29 @@
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J9" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
@@ -2241,44 +2241,44 @@
         <v>4.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G10" t="n">
         <v>2.36</v>
@@ -2318,7 +2318,7 @@
         <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2333,28 +2333,28 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
         <v>1.37</v>
@@ -2369,7 +2369,7 @@
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
         <v>500</v>
@@ -2399,7 +2399,7 @@
         <v>290</v>
       </c>
       <c r="AJ10" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="n">
         <v>75</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2426,7 +2426,7 @@
         <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
@@ -2438,19 +2438,19 @@
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
@@ -2459,20 +2459,20 @@
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE10" t="n">
         <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -2566,13 +2566,13 @@
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
         <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2584,7 +2584,7 @@
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.65</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>9</v>
+        <v>2.68</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2697,40 +2697,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="O12" t="n">
         <v>1.62</v>
       </c>
       <c r="P12" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
         <v>1.16</v>
@@ -2739,25 +2739,25 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
         <v>500</v>
@@ -2769,7 +2769,7 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
         <v>230</v>
@@ -2781,13 +2781,13 @@
         <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
-        <v>540</v>
+        <v>440</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
         <v>36</v>
@@ -2805,7 +2805,7 @@
         <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>9.199999999999999</v>
@@ -2814,10 +2814,10 @@
         <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
@@ -2826,19 +2826,19 @@
         <v>17.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -2847,20 +2847,20 @@
         <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2891,40 +2891,40 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G13" t="n">
         <v>1.57</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
         <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
@@ -2933,7 +2933,7 @@
         <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="U13" t="n">
         <v>1.53</v>
@@ -2945,79 +2945,79 @@
         <v>2.74</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
       </c>
       <c r="Z13" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AB13" t="n">
         <v>5.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF13" t="n">
         <v>7.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AN13" t="n">
         <v>15</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AP13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR13" t="n">
         <v>60</v>
       </c>
       <c r="AS13" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
         <v>48</v>
@@ -3029,10 +3029,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB13" t="n">
         <v>12</v>
@@ -3044,17 +3044,17 @@
         <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="BF13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
         <v>55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3085,31 +3085,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H14" t="n">
         <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="M14" t="n">
         <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.6</v>
@@ -3118,13 +3118,13 @@
         <v>1.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T14" t="n">
         <v>2.06</v>
@@ -3133,10 +3133,10 @@
         <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
         <v>17</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>5.1</v>
@@ -3202,7 +3202,7 @@
         <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
@@ -3214,7 +3214,7 @@
         <v>6.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
         <v>6.2</v>
@@ -3223,10 +3223,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="BB14" t="n">
         <v>7.2</v>
@@ -3235,7 +3235,7 @@
         <v>7</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BE14" t="n">
         <v>5.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>1.87</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -3297,31 +3297,31 @@
         <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
         <v>1.89</v>
@@ -3330,7 +3330,7 @@
         <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
         <v>90</v>
@@ -3369,10 +3369,10 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3390,13 +3390,13 @@
         <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="AT15" t="n">
         <v>4.4</v>
@@ -3405,7 +3405,7 @@
         <v>4.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW15" t="n">
         <v>2.84</v>
@@ -3417,19 +3417,19 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA15" t="n">
         <v>2.84</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BE15" t="n">
         <v>3.15</v>
@@ -3438,11 +3438,11 @@
         <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H16" t="n">
         <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
         <v>3.15</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P16" t="n">
         <v>1.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T16" t="n">
         <v>2.08</v>
@@ -3521,25 +3521,25 @@
         <v>1.85</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="n">
         <v>8.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA16" t="n">
         <v>120</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC16" t="n">
         <v>7.2</v>
@@ -3548,7 +3548,7 @@
         <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
         <v>20</v>
@@ -3560,13 +3560,13 @@
         <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
         <v>210</v>
       </c>
       <c r="AK16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,10 +3575,10 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
         <v>8.199999999999999</v>
@@ -3590,7 +3590,7 @@
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AT16" t="n">
         <v>8.199999999999999</v>
@@ -3599,10 +3599,10 @@
         <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX16" t="n">
         <v>17.5</v>
@@ -3614,29 +3614,29 @@
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>11.5</v>
       </c>
-      <c r="BB16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G17" t="n">
         <v>1.92</v>
@@ -3685,28 +3685,28 @@
         <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
         <v>1.96</v>
@@ -3781,13 +3781,13 @@
         <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
         <v>10.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
@@ -3799,13 +3799,13 @@
         <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA17" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3861,64 +3861,64 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J18" t="n">
         <v>2.94</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.92</v>
       </c>
       <c r="K18" t="n">
         <v>3.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P18" t="n">
         <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R18" t="n">
         <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
         <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
         <v>1.45</v>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z18" t="n">
         <v>20</v>
@@ -3978,7 +3978,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -3990,7 +3990,7 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="AX18" t="n">
         <v>16.5</v>
@@ -3999,32 +3999,32 @@
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC18" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
         <v>36</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -4055,64 +4055,64 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H19" t="n">
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
         <v>55</v>
@@ -4121,16 +4121,16 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="n">
         <v>10.5</v>
@@ -4139,13 +4139,13 @@
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -4160,7 +4160,7 @@
         <v>13.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP19" t="n">
         <v>10.5</v>
@@ -4169,10 +4169,10 @@
         <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4184,19 +4184,19 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX19" t="n">
         <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB19" t="n">
         <v>15</v>
@@ -4205,20 +4205,20 @@
         <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF19" t="n">
         <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -4249,31 +4249,31 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H20" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
         <v>3.35</v>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="n">
         <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O20" t="n">
         <v>1.71</v>
@@ -4282,13 +4282,13 @@
         <v>1.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
         <v>1.14</v>
       </c>
       <c r="S20" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="T20" t="n">
         <v>2.72</v>
@@ -4300,19 +4300,19 @@
         <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA20" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB20" t="n">
         <v>5.2</v>
@@ -4321,7 +4321,7 @@
         <v>8.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
@@ -4330,13 +4330,13 @@
         <v>8.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>40</v>
       </c>
       <c r="AI20" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AJ20" t="n">
         <v>21</v>
@@ -4354,19 +4354,19 @@
         <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>530</v>
+        <v>450</v>
       </c>
       <c r="AP20" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>26</v>
       </c>
       <c r="AS20" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
         <v>4.9</v>
@@ -4375,7 +4375,7 @@
         <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
         <v>44</v>
@@ -4405,14 +4405,14 @@
         <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG20" t="n">
         <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -4476,13 +4476,13 @@
         <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -760,10 +760,10 @@
         <v>3.55</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
         <v>2.4</v>
@@ -775,19 +775,19 @@
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>2.3</v>
@@ -802,13 +802,13 @@
         <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -817,7 +817,7 @@
         <v>8.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
         <v>120</v>
@@ -832,7 +832,7 @@
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
         <v>85</v>
@@ -850,16 +850,16 @@
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AO2" t="n">
         <v>46</v>
@@ -871,16 +871,16 @@
         <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
         <v>13</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
@@ -889,38 +889,38 @@
         <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC2" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
         <v>50</v>
       </c>
       <c r="BE2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H3" t="n">
         <v>1.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
@@ -978,10 +978,10 @@
         <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
         <v>2.5</v>
@@ -993,10 +993,10 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>2.04</v>
@@ -1008,7 +1008,7 @@
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
         <v>970</v>
@@ -1020,13 +1020,13 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>500</v>
@@ -1062,59 +1062,59 @@
         <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AW3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AX3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AY3" t="n">
         <v>18.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
         <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
         <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
         <v>3.55</v>
@@ -1169,7 +1169,7 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O4" t="n">
         <v>1.5</v>
@@ -1193,10 +1193,10 @@
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
@@ -1256,59 +1256,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR4" t="n">
         <v>1.78</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AX4" t="n">
         <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ4" t="n">
         <v>3.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="BF4" t="n">
         <v>1.72</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I5" t="n">
         <v>15.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.75</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W5" t="n">
         <v>3.5</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.55</v>
-      </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>80</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>500</v>
       </c>
       <c r="AC5" t="n">
         <v>42</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,7 +1450,7 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR5" t="n">
         <v>4.2</v>
@@ -1459,7 +1459,7 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
@@ -1471,13 +1471,13 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.8</v>
+        <v>2.64</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1486,23 +1486,23 @@
         <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -1557,19 +1557,19 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
         <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1578,7 +1578,7 @@
         <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -1590,16 +1590,16 @@
         <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="AA6" t="n">
         <v>300</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
@@ -1611,7 +1611,7 @@
         <v>160</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1623,80 +1623,80 @@
         <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK6" t="n">
         <v>19.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>290</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>17.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="AS6" t="n">
         <v>9.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY6" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC6" t="n">
         <v>15.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
         <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.54</v>
@@ -1751,16 +1751,16 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
@@ -1775,10 +1775,10 @@
         <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1790,16 +1790,16 @@
         <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
         <v>2.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="BD7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BF7" t="n">
         <v>2.32</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.3</v>
       </c>
       <c r="BG7" t="n">
         <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
@@ -1945,25 +1945,25 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
         <v>2.06</v>
@@ -1972,7 +1972,7 @@
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="X8" t="n">
         <v>25</v>
@@ -1984,13 +1984,13 @@
         <v>540</v>
       </c>
       <c r="AA8" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>34</v>
@@ -2002,13 +2002,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
         <v>12</v>
@@ -2020,25 +2020,25 @@
         <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
         <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
         <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AS8" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2050,10 +2050,10 @@
         <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
         <v>9.4</v>
@@ -2062,7 +2062,7 @@
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
         <v>11</v>
@@ -2071,20 +2071,20 @@
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BF8" t="n">
         <v>4.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H9" t="n">
         <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
         <v>3.05</v>
@@ -2139,13 +2139,13 @@
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
         <v>2.76</v>
@@ -2157,13 +2157,13 @@
         <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2223,7 +2223,7 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.9</v>
@@ -2232,7 +2232,7 @@
         <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
@@ -2244,41 +2244,41 @@
         <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>3.55</v>
@@ -2333,7 +2333,7 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
@@ -2342,7 +2342,7 @@
         <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
@@ -2351,10 +2351,10 @@
         <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
         <v>1.37</v>
@@ -2363,7 +2363,7 @@
         <v>1.73</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
@@ -2381,7 +2381,7 @@
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AE10" t="n">
         <v>140</v>
@@ -2393,13 +2393,13 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
         <v>290</v>
       </c>
       <c r="AJ10" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
         <v>75</v>
@@ -2423,10 +2423,10 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
@@ -2438,19 +2438,19 @@
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
@@ -2459,20 +2459,20 @@
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE10" t="n">
         <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J11" t="n">
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
@@ -2545,19 +2545,19 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
         <v>1.76</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
         <v>1000</v>
@@ -2566,7 +2566,7 @@
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
         <v>500</v>
@@ -2578,10 +2578,10 @@
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
         <v>50</v>
@@ -2590,13 +2590,13 @@
         <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,19 +2611,19 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.4</v>
+        <v>2.98</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
         <v>4.9</v>
@@ -2632,41 +2632,41 @@
         <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>8</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BD11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE11" t="n">
         <v>3.05</v>
       </c>
-      <c r="BE11" t="n">
-        <v>2.56</v>
-      </c>
       <c r="BF11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
@@ -2709,28 +2709,28 @@
         <v>4.7</v>
       </c>
       <c r="J12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
         <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1.16</v>
@@ -2739,10 +2739,10 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
         <v>1.27</v>
@@ -2751,7 +2751,7 @@
         <v>1.81</v>
       </c>
       <c r="X12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y12" t="n">
         <v>11</v>
@@ -2775,10 +2775,10 @@
         <v>230</v>
       </c>
       <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>29</v>
@@ -2787,19 +2787,19 @@
         <v>440</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
         <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AM12" t="n">
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
         <v>500</v>
@@ -2814,7 +2814,7 @@
         <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT12" t="n">
         <v>5.6</v>
@@ -2823,10 +2823,10 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2835,10 +2835,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -2847,20 +2847,20 @@
         <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H13" t="n">
         <v>8.4</v>
@@ -2903,7 +2903,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
@@ -2912,10 +2912,10 @@
         <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O13" t="n">
         <v>1.55</v>
@@ -2930,22 +2930,22 @@
         <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="T13" t="n">
         <v>2.68</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V13" t="n">
         <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
@@ -2954,10 +2954,10 @@
         <v>80</v>
       </c>
       <c r="AA13" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
         <v>75</v>
       </c>
       <c r="AM13" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="AN13" t="n">
         <v>15</v>
@@ -2999,28 +2999,28 @@
         <v>570</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AS13" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AW13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX13" t="n">
         <v>6.6</v>
@@ -3029,19 +3029,19 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BA13" t="n">
         <v>55</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BE13" t="n">
         <v>100</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="G14" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J14" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N14" t="n">
         <v>2.6</v>
@@ -3124,7 +3124,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T14" t="n">
         <v>2.06</v>
@@ -3133,10 +3133,10 @@
         <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X14" t="n">
         <v>17</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>5.1</v>
@@ -3202,19 +3202,19 @@
         <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
       </c>
       <c r="AU14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV14" t="n">
         <v>6</v>
       </c>
-      <c r="AV14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="AX14" t="n">
         <v>6.2</v>
@@ -3223,32 +3223,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
         <v>5.3</v>
@@ -3309,7 +3309,7 @@
         <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
         <v>2.16</v>
@@ -3390,13 +3390,13 @@
         <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AT15" t="n">
         <v>4.4</v>
@@ -3408,7 +3408,7 @@
         <v>6.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="AX15" t="n">
         <v>5.6</v>
@@ -3417,32 +3417,32 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BF15" t="n">
         <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J16" t="n">
         <v>3.05</v>
@@ -3506,10 +3506,10 @@
         <v>1.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
         <v>5.3</v>
@@ -3527,7 +3527,7 @@
         <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y16" t="n">
         <v>8.4</v>
@@ -3617,26 +3617,26 @@
         <v>50</v>
       </c>
       <c r="BB16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="BE16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF16" t="n">
         <v>12.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.79</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H17" t="n">
         <v>5.2</v>
@@ -3694,7 +3694,7 @@
         <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
         <v>1.79</v>
@@ -3712,10 +3712,10 @@
         <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
         <v>2.08</v>
@@ -3778,10 +3778,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
         <v>10.5</v>
@@ -3811,13 +3811,13 @@
         <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE17" t="n">
         <v>10.5</v>
@@ -3826,11 +3826,11 @@
         <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v>2.96</v>
       </c>
       <c r="J18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K18" t="n">
         <v>3.1</v>
@@ -4017,14 +4017,14 @@
         <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
         <v>36</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H19" t="n">
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.45</v>
@@ -4100,13 +4100,13 @@
         <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>1.82</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
         <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.7</v>
@@ -4276,13 +4276,13 @@
         <v>2.34</v>
       </c>
       <c r="O20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="P20" t="n">
         <v>1.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.14</v>
@@ -4291,7 +4291,7 @@
         <v>7.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="U20" t="n">
         <v>1.53</v>
@@ -4300,7 +4300,7 @@
         <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X20" t="n">
         <v>7</v>
@@ -4309,16 +4309,16 @@
         <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AA20" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
@@ -4327,7 +4327,7 @@
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -4336,7 +4336,7 @@
         <v>40</v>
       </c>
       <c r="AI20" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AJ20" t="n">
         <v>21</v>
@@ -4348,13 +4348,13 @@
         <v>95</v>
       </c>
       <c r="AM20" t="n">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="AN20" t="n">
         <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AP20" t="n">
         <v>6.4</v>
@@ -4363,7 +4363,7 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS20" t="n">
         <v>48</v>
@@ -4372,10 +4372,10 @@
         <v>4.9</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW20" t="n">
         <v>44</v>
@@ -4396,7 +4396,7 @@
         <v>17.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BD20" t="n">
         <v>38</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>980</v>
       </c>
       <c r="J21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -757,31 +757,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G2" t="n">
         <v>3.75</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.43</v>
@@ -790,137 +790,137 @@
         <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
         <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="n">
-        <v>230</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BD2" t="n">
         <v>50</v>
       </c>
       <c r="BE2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.54</v>
@@ -975,52 +975,52 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
         <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
@@ -1059,62 +1059,62 @@
         <v>500</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
         <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
         <v>2.74</v>
@@ -1154,10 +1154,10 @@
         <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
         <v>3.25</v>
@@ -1169,16 +1169,16 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
@@ -1193,7 +1193,7 @@
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
         <v>1.58</v>
@@ -1235,13 +1235,13 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK4" t="n">
         <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.78</v>
+        <v>2.94</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.76</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
         <v>5.7</v>
       </c>
       <c r="AZ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD4" t="n">
         <v>3.2</v>
       </c>
-      <c r="BA4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BE4" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.72</v>
+        <v>5.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H5" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
         <v>80</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
         <v>42</v>
@@ -1417,13 +1417,13 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1435,25 +1435,25 @@
         <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
@@ -1465,44 +1465,44 @@
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>29</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.64</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1533,40 +1533,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
         <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.28</v>
@@ -1575,34 +1575,34 @@
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
         <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="AA6" t="n">
         <v>300</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>32</v>
@@ -1611,7 +1611,7 @@
         <v>160</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1626,7 +1626,7 @@
         <v>15.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>48</v>
@@ -1635,7 +1635,7 @@
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO6" t="n">
         <v>290</v>
@@ -1650,19 +1650,19 @@
         <v>23</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>7.6</v>
@@ -1674,29 +1674,29 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF6" t="n">
         <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1727,70 +1727,70 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
@@ -1799,7 +1799,7 @@
         <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV7" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BG7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.39</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
         <v>5.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.29</v>
@@ -1945,64 +1945,64 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
         <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z8" t="n">
-        <v>540</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -2017,10 +2017,10 @@
         <v>13.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AN8" t="n">
         <v>5</v>
@@ -2032,16 +2032,16 @@
         <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR8" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>11.5</v>
@@ -2050,41 +2050,41 @@
         <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
         <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2118,25 +2118,25 @@
         <v>2.72</v>
       </c>
       <c r="G9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
         <v>2.82</v>
       </c>
       <c r="K9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
         <v>2.6</v>
@@ -2157,10 +2157,10 @@
         <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
         <v>1.42</v>
@@ -2169,7 +2169,7 @@
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
@@ -2241,44 +2241,44 @@
         <v>4.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>1.46</v>
@@ -2333,34 +2333,34 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2369,16 +2369,16 @@
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
         <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
         <v>27</v>
@@ -2387,22 +2387,22 @@
         <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
         <v>180</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2423,56 +2423,56 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
         <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2503,46 +2503,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H11" t="n">
         <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
         <v>1.89</v>
@@ -2551,22 +2551,22 @@
         <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>500</v>
@@ -2578,7 +2578,7 @@
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
         <v>500</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.98</v>
+        <v>4.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.66</v>
@@ -2721,16 +2721,16 @@
         <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O12" t="n">
         <v>1.64</v>
       </c>
       <c r="P12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
         <v>1.16</v>
@@ -2739,16 +2739,16 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X12" t="n">
         <v>7.8</v>
@@ -2757,7 +2757,7 @@
         <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
         <v>500</v>
@@ -2778,7 +2778,7 @@
         <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
         <v>29</v>
@@ -2814,16 +2814,16 @@
         <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="AT12" t="n">
         <v>5.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW12" t="n">
         <v>10</v>
@@ -2838,29 +2838,29 @@
         <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF12" t="n">
         <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.58</v>
@@ -2915,7 +2915,7 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
         <v>1.55</v>
@@ -2924,7 +2924,7 @@
         <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
@@ -2933,7 +2933,7 @@
         <v>5.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
         <v>1.54</v>
@@ -2942,7 +2942,7 @@
         <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X13" t="n">
         <v>9.4</v>
@@ -2960,7 +2960,7 @@
         <v>5.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
         <v>38</v>
@@ -2978,7 +2978,7 @@
         <v>42</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AJ13" t="n">
         <v>14</v>
@@ -2999,16 +2999,16 @@
         <v>570</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS13" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
@@ -3041,20 +3041,20 @@
         <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF13" t="n">
         <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G14" t="n">
         <v>2.64</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>2.98</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>1.59</v>
@@ -3118,7 +3118,7 @@
         <v>1.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
@@ -3133,16 +3133,16 @@
         <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
         <v>1.62</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.98</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
         <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.98</v>
+        <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
         <v>5.3</v>
@@ -3312,7 +3312,7 @@
         <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.29</v>
@@ -3324,7 +3324,7 @@
         <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V15" t="n">
         <v>1.23</v>
@@ -3393,7 +3393,7 @@
         <v>5.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AS15" t="n">
         <v>2.2</v>
@@ -3417,19 +3417,19 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA15" t="n">
         <v>2.94</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE15" t="n">
         <v>3.35</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>2.78</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P16" t="n">
         <v>1.58</v>
@@ -3524,7 +3524,7 @@
         <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
         <v>9.199999999999999</v>
@@ -3536,7 +3536,7 @@
         <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AB16" t="n">
         <v>9.4</v>
@@ -3548,10 +3548,10 @@
         <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
         <v>14.5</v>
@@ -3614,29 +3614,29 @@
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
         <v>55</v>
       </c>
       <c r="BE16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
         <v>1.91</v>
@@ -3676,13 +3676,13 @@
         <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.45</v>
@@ -3781,7 +3781,7 @@
         <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS17" t="n">
         <v>10.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J18" t="n">
         <v>2.96</v>
@@ -3879,16 +3879,16 @@
         <v>3.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M18" t="n">
         <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
         <v>1.54</v>
@@ -3897,7 +3897,7 @@
         <v>2.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>5.6</v>
@@ -3909,7 +3909,7 @@
         <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
         <v>1.45</v>
@@ -3945,34 +3945,34 @@
         <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI18" t="n">
         <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR18" t="n">
         <v>15</v>
@@ -3999,7 +3999,7 @@
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BA18" t="n">
         <v>7.2</v>
@@ -4008,23 +4008,23 @@
         <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
         <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BG18" t="n">
         <v>36</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -4064,46 +4064,46 @@
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
         <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
         <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
         <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
         <v>2.28</v>
@@ -4115,7 +4115,7 @@
         <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -4145,7 +4145,7 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -4172,7 +4172,7 @@
         <v>6.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4184,7 +4184,7 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX19" t="n">
         <v>8.4</v>
@@ -4196,7 +4196,7 @@
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
         <v>15</v>
@@ -4205,20 +4205,20 @@
         <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
         <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>1.86</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
         <v>6.6</v>
@@ -4264,7 +4264,7 @@
         <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
         <v>1.7</v>
@@ -4273,7 +4273,7 @@
         <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
         <v>1.72</v>
@@ -4291,7 +4291,7 @@
         <v>7.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
         <v>1.53</v>
@@ -4303,7 +4303,7 @@
         <v>2.16</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y20" t="n">
         <v>13.5</v>
@@ -4318,7 +4318,7 @@
         <v>5.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
@@ -4330,7 +4330,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>40</v>
@@ -4348,7 +4348,7 @@
         <v>95</v>
       </c>
       <c r="AM20" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AN20" t="n">
         <v>27</v>
@@ -4360,22 +4360,22 @@
         <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS20" t="n">
         <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU20" t="n">
         <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW20" t="n">
         <v>44</v>
@@ -4390,7 +4390,7 @@
         <v>32</v>
       </c>
       <c r="BA20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB20" t="n">
         <v>17.5</v>
@@ -4405,14 +4405,14 @@
         <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BG20" t="n">
         <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G21" t="n">
         <v>970</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I21" t="n">
         <v>980</v>
@@ -4485,7 +4485,7 @@
         <v>1.79</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -760,13 +760,13 @@
         <v>3.65</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -778,7 +778,7 @@
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
         <v>3.2</v>
@@ -787,10 +787,10 @@
         <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
         <v>1.26</v>
@@ -802,28 +802,28 @@
         <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
         <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
         <v>7.2</v>
@@ -832,28 +832,28 @@
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
         <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
         <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
         <v>75</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>450</v>
@@ -865,37 +865,37 @@
         <v>26</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
         <v>40</v>
@@ -904,23 +904,23 @@
         <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD2" t="n">
         <v>50</v>
       </c>
       <c r="BE2" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG2" t="n">
         <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF3" t="n">
         <v>36</v>
       </c>
-      <c r="AE3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>500</v>
-      </c>
       <c r="AG3" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AK3" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AL3" t="n">
         <v>700</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.15</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>2.94</v>
@@ -1172,43 +1172,43 @@
         <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
         <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
         <v>1000</v>
@@ -1220,7 +1220,7 @@
         <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
@@ -1235,13 +1235,13 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF4" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG4" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
         <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
         <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>540</v>
+        <v>110</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AB5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
         <v>13</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AQ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA5" t="n">
         <v>42</v>
       </c>
-      <c r="AD5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.48</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H6" t="n">
         <v>7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1560,143 +1560,143 @@
         <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
         <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE6" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>12.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
         <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
         <v>23</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BF6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
         <v>1.98</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>14</v>
       </c>
-      <c r="AD7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BE7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1921,37 +1921,37 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
         <v>1.39</v>
       </c>
       <c r="H8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
         <v>5.9</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q8" t="n">
         <v>1.58</v>
@@ -1960,31 +1960,31 @@
         <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
         <v>3.55</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
-        <v>350</v>
+        <v>990</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
@@ -1993,34 +1993,34 @@
         <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
         <v>9.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM8" t="n">
         <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>390</v>
       </c>
       <c r="AN8" t="n">
         <v>5</v>
@@ -2032,59 +2032,59 @@
         <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW8" t="n">
-        <v>16.5</v>
+        <v>100</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE8" t="n">
         <v>85</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H9" t="n">
         <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
         <v>90</v>
@@ -2208,7 +2208,7 @@
         <v>230</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.54</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
@@ -2241,44 +2241,44 @@
         <v>4.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.46</v>
+        <v>10.5</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.86</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.54</v>
+        <v>3.85</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.72</v>
+        <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
         <v>3.45</v>
@@ -2333,34 +2333,34 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2369,13 +2369,13 @@
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
         <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>7.6</v>
@@ -2387,22 +2387,22 @@
         <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AG10" t="n">
         <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ10" t="n">
         <v>130</v>
       </c>
       <c r="AK10" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="n">
         <v>180</v>
@@ -2411,34 +2411,34 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2450,29 +2450,29 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC10" t="n">
         <v>17.5</v>
       </c>
-      <c r="BC10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD10" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
         <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>2.34</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
         <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -2545,13 +2545,13 @@
         <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
         <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
         <v>1.75</v>
@@ -2566,13 +2566,13 @@
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="AB11" t="n">
         <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2620,19 +2620,19 @@
         <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
         <v>11.5</v>
@@ -2641,32 +2641,32 @@
         <v>7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="BC11" t="n">
         <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF11" t="n">
         <v>10</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
         <v>1.15</v>
@@ -2724,10 +2724,10 @@
         <v>2.46</v>
       </c>
       <c r="O12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q12" t="n">
         <v>2.92</v>
@@ -2739,128 +2739,128 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU12" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AV12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>21</v>
       </c>
-      <c r="AE12" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="BA12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>29</v>
       </c>
-      <c r="AI12" t="n">
-        <v>440</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>210</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>3.95</v>
@@ -2909,7 +2909,7 @@
         <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
@@ -2942,7 +2942,7 @@
         <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X13" t="n">
         <v>9.4</v>
@@ -2954,13 +2954,13 @@
         <v>80</v>
       </c>
       <c r="AA13" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="AB13" t="n">
         <v>5.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
         <v>38</v>
@@ -2972,10 +2972,10 @@
         <v>7.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="n">
         <v>260</v>
@@ -2984,34 +2984,34 @@
         <v>14</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
         <v>75</v>
       </c>
       <c r="AM13" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
         <v>15</v>
       </c>
       <c r="AO13" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="AP13" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS13" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AT13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU13" t="n">
         <v>8.800000000000001</v>
@@ -3023,7 +3023,7 @@
         <v>55</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
@@ -3032,13 +3032,13 @@
         <v>36</v>
       </c>
       <c r="BA13" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
         <v>60</v>
@@ -3047,14 +3047,14 @@
         <v>110</v>
       </c>
       <c r="BF13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L14" t="n">
         <v>1.59</v>
@@ -3127,16 +3127,16 @@
         <v>5.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
         <v>90</v>
@@ -3148,10 +3148,10 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
         <v>14</v>
@@ -3175,13 +3175,13 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR14" t="n">
         <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -3324,7 +3324,7 @@
         <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
         <v>1.23</v>
@@ -3372,7 +3372,7 @@
         <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3393,10 +3393,10 @@
         <v>5.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AT15" t="n">
         <v>4.4</v>
@@ -3408,7 +3408,7 @@
         <v>6.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.94</v>
+        <v>5.1</v>
       </c>
       <c r="AX15" t="n">
         <v>5.6</v>
@@ -3417,10 +3417,10 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.94</v>
+        <v>5.5</v>
       </c>
       <c r="BB15" t="n">
         <v>6.4</v>
@@ -3429,20 +3429,20 @@
         <v>5.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BF15" t="n">
         <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.94</v>
+        <v>5.1</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>3.05</v>
@@ -3491,13 +3491,13 @@
         <v>3.15</v>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
         <v>1.52</v>
@@ -3518,13 +3518,13 @@
         <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
         <v>9.199999999999999</v>
@@ -3539,7 +3539,7 @@
         <v>44</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>7.2</v>
@@ -3548,7 +3548,7 @@
         <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
         <v>21</v>
@@ -3590,7 +3590,7 @@
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
         <v>8.199999999999999</v>
@@ -3599,7 +3599,7 @@
         <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
         <v>32</v>
@@ -3614,29 +3614,29 @@
         <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD16" t="n">
         <v>55</v>
       </c>
       <c r="BE16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="I18" t="n">
         <v>2.92</v>
       </c>
       <c r="J18" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L18" t="n">
         <v>1.59</v>
@@ -3912,7 +3912,7 @@
         <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
         <v>9.800000000000001</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
       </c>
       <c r="T19" t="n">
         <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>110</v>
       </c>
       <c r="AF19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.4</v>
+        <v>75</v>
       </c>
       <c r="AX19" t="n">
         <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BB19" t="n">
         <v>15</v>
       </c>
       <c r="BC19" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -4255,19 +4255,19 @@
         <v>1.86</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
         <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
         <v>1.16</v>
@@ -4282,7 +4282,7 @@
         <v>1.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
         <v>1.14</v>
@@ -4291,10 +4291,10 @@
         <v>7.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V20" t="n">
         <v>1.17</v>
@@ -4303,76 +4303,76 @@
         <v>2.16</v>
       </c>
       <c r="X20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
         <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA20" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI20" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AJ20" t="n">
         <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM20" t="n">
+        <v>480</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO20" t="n">
         <v>450</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>430</v>
       </c>
       <c r="AP20" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AS20" t="n">
         <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU20" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
         <v>26</v>
@@ -4384,7 +4384,7 @@
         <v>7.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>32</v>
@@ -4393,26 +4393,26 @@
         <v>50</v>
       </c>
       <c r="BB20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
         <v>26</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BE20" t="n">
         <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG20" t="n">
         <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>970</v>
       </c>
       <c r="H21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
         <v>980</v>
@@ -4464,7 +4464,7 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>1.25</v>
@@ -4488,7 +4488,7 @@
         <v>1.74</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J2" t="n">
         <v>2.56</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.58</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
         <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="P2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
         <v>2.26</v>
@@ -805,7 +805,7 @@
         <v>1.57</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
         <v>1.47</v>
@@ -823,7 +823,7 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
         <v>7.6</v>
@@ -835,10 +835,10 @@
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
         <v>32</v>
@@ -865,62 +865,62 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BD2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF2" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BG2" t="n">
         <v>5.5</v>
       </c>
-      <c r="BF2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
         <v>3.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.7</v>
@@ -975,40 +975,40 @@
         <v>1.19</v>
       </c>
       <c r="N3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
         <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
         <v>1.54</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -1017,10 +1017,10 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
         <v>500</v>
@@ -1059,7 +1059,7 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
@@ -1068,7 +1068,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="AT3" t="n">
         <v>5.4</v>
@@ -1080,7 +1080,7 @@
         <v>6.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
@@ -1089,32 +1089,32 @@
         <v>5.7</v>
       </c>
       <c r="AZ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BC3" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
         <v>5.8</v>
@@ -1160,49 +1160,49 @@
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
         <v>95</v>
@@ -1211,10 +1211,10 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
         <v>23</v>
@@ -1241,74 +1241,74 @@
         <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU4" t="n">
         <v>4</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>1.58</v>
@@ -1372,16 +1372,16 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R5" t="n">
         <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
@@ -1390,7 +1390,7 @@
         <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AS5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV5" t="n">
         <v>2.16</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.32</v>
       </c>
       <c r="AW5" t="n">
         <v>2.12</v>
       </c>
       <c r="AX5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY5" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BG5" t="n">
         <v>2.12</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
         <v>3.45</v>
       </c>
       <c r="H6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I6" t="n">
         <v>3.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
         <v>1.76</v>
       </c>
       <c r="M6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="P6" t="n">
         <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T6" t="n">
         <v>2.34</v>
@@ -1581,7 +1581,7 @@
         <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
         <v>1.42</v>
@@ -1659,7 +1659,7 @@
         <v>5.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>5.8</v>
@@ -1668,10 +1668,10 @@
         <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
         <v>6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1736,25 +1736,25 @@
         <v>2.32</v>
       </c>
       <c r="I7" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P7" t="n">
         <v>1.33</v>
@@ -1769,13 +1769,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
         <v>1.54</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
         <v>1.29</v>
@@ -1847,7 +1847,7 @@
         <v>5.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
         <v>5.8</v>
@@ -1859,10 +1859,10 @@
         <v>5.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>5</v>
@@ -1874,7 +1874,7 @@
         <v>5.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
         <v>5.7</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
         <v>1.5</v>
@@ -1951,40 +1951,40 @@
         <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
         <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
         <v>11.5</v>
@@ -1993,55 +1993,55 @@
         <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AM8" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
@@ -2059,16 +2059,16 @@
         <v>13.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BB8" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
@@ -2077,14 +2077,14 @@
         <v>16.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="BG8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.51</v>
@@ -2139,7 +2139,7 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>1.46</v>
@@ -2148,70 +2148,70 @@
         <v>1.69</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
         <v>4.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AK9" t="n">
         <v>85</v>
       </c>
       <c r="AL9" t="n">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2220,65 +2220,65 @@
         <v>700</v>
       </c>
       <c r="AO9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD9" t="n">
         <v>17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>16</v>
       </c>
       <c r="BE9" t="n">
         <v>48</v>
       </c>
       <c r="BF9" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="BG9" t="n">
         <v>17.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2309,37 +2309,37 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
         <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K10" t="n">
         <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
         <v>2.56</v>
@@ -2348,7 +2348,7 @@
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T10" t="n">
         <v>2.02</v>
@@ -2384,7 +2384,7 @@
         <v>500</v>
       </c>
       <c r="AE10" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
         <v>38</v>
@@ -2456,7 +2456,7 @@
         <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>8.4</v>
@@ -2465,14 +2465,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="G11" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="H11" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="Z11" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AA11" t="n">
-        <v>550</v>
+        <v>390</v>
       </c>
       <c r="AB11" t="n">
         <v>7.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AE11" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AF11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX11" t="n">
         <v>7</v>
       </c>
-      <c r="AG11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>400</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA11" t="n">
         <v>42</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L12" t="n">
         <v>1.44</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.42</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -2724,73 +2724,73 @@
         <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Z12" t="n">
-        <v>160</v>
+        <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>580</v>
+        <v>430</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AF12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>32</v>
       </c>
       <c r="AI12" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
@@ -2799,68 +2799,68 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO12" t="n">
-        <v>490</v>
+        <v>310</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>90</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
         <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BE12" t="n">
         <v>36</v>
       </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>1.89</v>
       </c>
       <c r="I13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -2909,7 +2909,7 @@
         <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
@@ -2930,73 +2930,73 @@
         <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
         <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="W13" t="n">
         <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
         <v>6.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB13" t="n">
         <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
         <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
         <v>23</v>
       </c>
       <c r="AH13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
         <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK13" t="n">
         <v>150</v>
       </c>
       <c r="AL13" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP13" t="n">
         <v>8.800000000000001</v>
@@ -3005,22 +3005,22 @@
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AV13" t="n">
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AX13" t="n">
         <v>34</v>
@@ -3035,26 +3035,26 @@
         <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE13" t="n">
         <v>28</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I14" t="n">
         <v>8.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9</v>
       </c>
       <c r="J14" t="n">
         <v>5.8</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3109,46 +3109,46 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R14" t="n">
         <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="X14" t="n">
         <v>30</v>
       </c>
       <c r="Y14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AB14" t="n">
         <v>10.5</v>
@@ -3157,22 +3157,22 @@
         <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
         <v>12.5</v>
@@ -3187,68 +3187,68 @@
         <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AO14" t="n">
         <v>140</v>
       </c>
       <c r="AP14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ14" t="n">
         <v>30</v>
       </c>
       <c r="AR14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS14" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AX14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
         <v>9</v>
       </c>
-      <c r="AY14" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC14" t="n">
         <v>12.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE14" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG14" t="n">
         <v>85</v>
       </c>
-      <c r="BF14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G15" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -3306,46 +3306,46 @@
         <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P15" t="n">
         <v>1.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V15" t="n">
         <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
         <v>320</v>
       </c>
       <c r="AB15" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AC15" t="n">
         <v>14</v>
@@ -3369,7 +3369,7 @@
         <v>450</v>
       </c>
       <c r="AJ15" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>50</v>
@@ -3381,7 +3381,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
@@ -3396,19 +3396,19 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>5.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AV15" t="n">
         <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
         <v>7.8</v>
@@ -3432,7 +3432,7 @@
         <v>8.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>8.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3473,100 +3473,100 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.35</v>
       </c>
-      <c r="K16" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
         <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="X16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y16" t="n">
         <v>11</v>
       </c>
-      <c r="Y16" t="n">
-        <v>12</v>
-      </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>7.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
@@ -3575,52 +3575,52 @@
         <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA16" t="n">
         <v>48</v>
       </c>
       <c r="BB16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC16" t="n">
         <v>29</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>26</v>
       </c>
       <c r="BD16" t="n">
         <v>38</v>
@@ -3629,14 +3629,14 @@
         <v>30</v>
       </c>
       <c r="BF16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BG16" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
         <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.67</v>
@@ -3691,10 +3691,10 @@
         <v>1.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P17" t="n">
         <v>1.46</v>
@@ -3706,25 +3706,25 @@
         <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T17" t="n">
         <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z17" t="n">
         <v>24</v>
@@ -3763,13 +3763,13 @@
         <v>42</v>
       </c>
       <c r="AL17" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AM17" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO17" t="n">
         <v>110</v>
@@ -3784,19 +3784,19 @@
         <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AT17" t="n">
         <v>6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
         <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
@@ -3805,32 +3805,32 @@
         <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BB17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="n">
         <v>34</v>
       </c>
       <c r="BD17" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BE17" t="n">
-        <v>17.5</v>
+        <v>46</v>
       </c>
       <c r="BF17" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="BG17" t="n">
         <v>40</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.5</v>
@@ -3885,7 +3885,7 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.41</v>
@@ -3912,49 +3912,49 @@
         <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="AB18" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AC18" t="n">
         <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3987,13 +3987,13 @@
         <v>6.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>9.800000000000001</v>
@@ -4002,7 +4002,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB18" t="n">
         <v>13.5</v>
@@ -4014,17 +4014,17 @@
         <v>28</v>
       </c>
       <c r="BE18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG18" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>9.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
@@ -4079,7 +4079,7 @@
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
         <v>1.55</v>
@@ -4094,31 +4094,31 @@
         <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T19" t="n">
         <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA19" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AB19" t="n">
         <v>5.4</v>
@@ -4127,28 +4127,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE19" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AF19" t="n">
         <v>7.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>70</v>
@@ -4160,7 +4160,7 @@
         <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP19" t="n">
         <v>8.6</v>
@@ -4169,7 +4169,7 @@
         <v>16.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS19" t="n">
         <v>110</v>
@@ -4181,10 +4181,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW19" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AX19" t="n">
         <v>6.8</v>
@@ -4193,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BA19" t="n">
         <v>110</v>
@@ -4205,10 +4205,10 @@
         <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE19" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.48</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H20" t="n">
         <v>3.45</v>
@@ -4261,22 +4261,22 @@
         <v>3.75</v>
       </c>
       <c r="J20" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
         <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N20" t="n">
         <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P20" t="n">
         <v>1.51</v>
@@ -4288,31 +4288,31 @@
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AA20" t="n">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="AB20" t="n">
         <v>13</v>
@@ -4321,19 +4321,19 @@
         <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4342,10 +4342,10 @@
         <v>160</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4357,10 +4357,10 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
         <v>10.5</v>
@@ -4378,41 +4378,41 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB20" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>13</v>
       </c>
       <c r="BC20" t="n">
         <v>15</v>
       </c>
       <c r="BD20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE20" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
         <v>6.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H21" t="n">
         <v>3.6</v>
@@ -4455,34 +4455,34 @@
         <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
         <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P21" t="n">
         <v>1.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R21" t="n">
         <v>1.14</v>
       </c>
       <c r="S21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T21" t="n">
         <v>2.26</v>
@@ -4491,13 +4491,13 @@
         <v>1.56</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
         <v>20</v>
@@ -4515,13 +4515,13 @@
         <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AE21" t="n">
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
         <v>500</v>
@@ -4557,10 +4557,10 @@
         <v>7.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>5.1</v>
@@ -4569,7 +4569,7 @@
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
         <v>7</v>
@@ -4578,13 +4578,13 @@
         <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB21" t="n">
         <v>14</v>
@@ -4596,17 +4596,17 @@
         <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="BF21" t="n">
         <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>4.2</v>
       </c>
       <c r="G22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J22" t="n">
         <v>3.2</v>
@@ -4667,7 +4667,7 @@
         <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
         <v>2.32</v>
@@ -4679,28 +4679,28 @@
         <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>1.84</v>
       </c>
       <c r="V22" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB22" t="n">
         <v>13.5</v>
@@ -4709,7 +4709,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4730,7 +4730,7 @@
         <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AL22" t="n">
         <v>500</v>
@@ -4778,29 +4778,29 @@
         <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
         <v>18.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
         <v>5.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.45</v>
@@ -4855,13 +4855,13 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q23" t="n">
         <v>2.12</v>
@@ -4873,22 +4873,22 @@
         <v>3.85</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V23" t="n">
         <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X23" t="n">
         <v>90</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>36</v>
@@ -4921,13 +4921,13 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
         <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4942,7 +4942,7 @@
         <v>5.7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR23" t="n">
         <v>22</v>
@@ -4951,16 +4951,16 @@
         <v>4.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX23" t="n">
         <v>5.6</v>
@@ -4972,7 +4972,7 @@
         <v>9.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB23" t="n">
         <v>9</v>
@@ -4984,17 +4984,17 @@
         <v>13.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.3</v>
+        <v>100</v>
       </c>
       <c r="BF23" t="n">
         <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -5031,16 +5031,16 @@
         <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J24" t="n">
         <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L24" t="n">
         <v>1.58</v>
@@ -5049,10 +5049,10 @@
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
         <v>1.58</v>
@@ -5061,10 +5061,10 @@
         <v>2.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T24" t="n">
         <v>2.08</v>
@@ -5076,13 +5076,13 @@
         <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z24" t="n">
         <v>15.5</v>
@@ -5109,16 +5109,16 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
         <v>210</v>
       </c>
       <c r="AK24" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AL24" t="n">
         <v>1000</v>
@@ -5142,7 +5142,7 @@
         <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AT24" t="n">
         <v>8.199999999999999</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AX24" t="n">
         <v>17.5</v>
@@ -5163,32 +5163,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC24" t="n">
         <v>11</v>
       </c>
-      <c r="BB24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>42</v>
-      </c>
       <c r="BD24" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="BE24" t="n">
-        <v>12.5</v>
+        <v>130</v>
       </c>
       <c r="BF24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -5228,13 +5228,13 @@
         <v>5.2</v>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
         <v>1.45</v>
@@ -5243,16 +5243,16 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
         <v>1.31</v>
@@ -5279,7 +5279,7 @@
         <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -5312,16 +5312,16 @@
         <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO25" t="n">
         <v>700</v>
@@ -5348,7 +5348,7 @@
         <v>18</v>
       </c>
       <c r="AW25" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
@@ -5369,20 +5369,20 @@
         <v>17.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="BF25" t="n">
         <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>2.86</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I26" t="n">
         <v>3.1</v>
@@ -5437,13 +5437,13 @@
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
         <v>1.55</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q26" t="n">
         <v>2.68</v>
@@ -5455,7 +5455,7 @@
         <v>5.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
         <v>1.81</v>
@@ -5464,7 +5464,7 @@
         <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
         <v>8.800000000000001</v>
@@ -5476,7 +5476,7 @@
         <v>20</v>
       </c>
       <c r="AA26" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
         <v>8.4</v>
@@ -5500,10 +5500,10 @@
         <v>38</v>
       </c>
       <c r="AI26" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AK26" t="n">
         <v>500</v>
@@ -5530,7 +5530,7 @@
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5545,28 +5545,28 @@
         <v>36</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BB26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE26" t="n">
-        <v>9.4</v>
+        <v>140</v>
       </c>
       <c r="BF26" t="n">
         <v>8.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H27" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
         <v>650</v>
@@ -5625,7 +5625,7 @@
         <v>750</v>
       </c>
       <c r="L27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
@@ -5637,16 +5637,16 @@
         <v>1.06</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S27" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -5658,7 +5658,7 @@
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G28" t="n">
         <v>1.76</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
         <v>3.8</v>
@@ -5855,7 +5855,7 @@
         <v>2.3</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y28" t="n">
         <v>19</v>
@@ -5864,7 +5864,7 @@
         <v>55</v>
       </c>
       <c r="AA28" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
         <v>7.6</v>
@@ -5882,7 +5882,7 @@
         <v>9.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>22</v>
@@ -5903,13 +5903,13 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO28" t="n">
         <v>140</v>
       </c>
       <c r="AP28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>16</v>
@@ -5918,7 +5918,7 @@
         <v>42</v>
       </c>
       <c r="AS28" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT28" t="n">
         <v>6.4</v>
@@ -5927,7 +5927,7 @@
         <v>7.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
         <v>75</v>
@@ -5942,7 +5942,7 @@
         <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
@@ -5951,20 +5951,20 @@
         <v>17.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BE28" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BF28" t="n">
         <v>11.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="G29" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
         <v>6.4</v>
       </c>
-      <c r="I29" t="n">
-        <v>6.6</v>
-      </c>
       <c r="J29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K29" t="n">
         <v>3.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.71</v>
@@ -6019,10 +6019,10 @@
         <v>1.16</v>
       </c>
       <c r="N29" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O29" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P29" t="n">
         <v>1.43</v>
@@ -6034,73 +6034,73 @@
         <v>1.14</v>
       </c>
       <c r="S29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W29" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="X29" t="n">
         <v>7.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA29" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AB29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE29" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
         <v>38</v>
       </c>
       <c r="AI29" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
         <v>32</v>
       </c>
       <c r="AL29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="n">
         <v>430</v>
       </c>
       <c r="AN29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO29" t="n">
-        <v>470</v>
+        <v>350</v>
       </c>
       <c r="AP29" t="n">
         <v>6.6</v>
@@ -6109,56 +6109,56 @@
         <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS29" t="n">
         <v>48</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU29" t="n">
         <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW29" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AX29" t="n">
         <v>7.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB29" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD29" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="BE29" t="n">
         <v>55</v>
       </c>
       <c r="BF29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG29" t="n">
         <v>55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="G30" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H30" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="I30" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O30" t="n">
         <v>1.27</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T30" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U30" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W30" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X30" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
         <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC30" t="n">
         <v>9</v>
       </c>
       <c r="AD30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR30" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
+      <c r="AS30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA30" t="n">
         <v>28</v>
       </c>
-      <c r="AO30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP30" t="n">
+      <c r="BB30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC30" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR30" t="n">
+      <c r="BD30" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE30" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -757,73 +757,73 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
         <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.26</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
         <v>7.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2" t="n">
         <v>7.6</v>
@@ -838,7 +838,7 @@
         <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
         <v>32</v>
@@ -853,7 +853,7 @@
         <v>150</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
@@ -865,62 +865,62 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="K3" t="n">
         <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M3" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="N3" t="n">
         <v>2.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
         <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
         <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>8.199999999999999</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
         <v>500</v>
@@ -1017,7 +1017,7 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
         <v>42</v>
@@ -1032,7 +1032,7 @@
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AH3" t="n">
         <v>500</v>
@@ -1062,59 +1062,59 @@
         <v>3.9</v>
       </c>
       <c r="AQ3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AU3" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV3" t="n">
         <v>6.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.6</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O4" t="n">
         <v>1.5</v>
@@ -1178,31 +1178,31 @@
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
         <v>95</v>
@@ -1214,10 +1214,10 @@
         <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
@@ -1229,7 +1229,7 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>700</v>
@@ -1247,68 +1247,68 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.6</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
         <v>2.22</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
         <v>5.4</v>
@@ -1354,13 +1354,13 @@
         <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.58</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
         <v>2.58</v>
@@ -1372,10 +1372,10 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
         <v>5.2</v>
@@ -1384,7 +1384,7 @@
         <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
         <v>1.25</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.12</v>
+        <v>3.95</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE5" t="n">
         <v>3.7</v>
       </c>
-      <c r="AV5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BF5" t="n">
-        <v>2.02</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="K6" t="n">
         <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
         <v>1.19</v>
@@ -1566,7 +1566,7 @@
         <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
@@ -1575,28 +1575,28 @@
         <v>7.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
         <v>8.6</v>
@@ -1605,7 +1605,7 @@
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>160</v>
@@ -1614,7 +1614,7 @@
         <v>22</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>34</v>
@@ -1626,7 +1626,7 @@
         <v>160</v>
       </c>
       <c r="AK6" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AL6" t="n">
         <v>500</v>
@@ -1641,62 +1641,62 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ6" t="n">
         <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU6" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.8</v>
+        <v>28</v>
       </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1730,55 +1730,55 @@
         <v>3.45</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
         <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>7.4</v>
@@ -1835,62 +1835,62 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT7" t="n">
         <v>4.8</v>
       </c>
       <c r="AU7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5</v>
-      </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.8</v>
       </c>
-      <c r="BF7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
@@ -1939,40 +1939,40 @@
         <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
         <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X8" t="n">
         <v>11</v>
@@ -1981,13 +1981,13 @@
         <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
         <v>7.2</v>
@@ -1996,37 +1996,37 @@
         <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AK8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL8" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP8" t="n">
         <v>9.800000000000001</v>
@@ -2035,13 +2035,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
@@ -2050,41 +2050,41 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
         <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
       </c>
       <c r="BE8" t="n">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="BF8" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BG8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H9" t="n">
         <v>2.08</v>
@@ -2127,43 +2127,43 @@
         <v>2.14</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
         <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.87</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.88</v>
       </c>
       <c r="W9" t="n">
         <v>1.3</v>
@@ -2178,13 +2178,13 @@
         <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
         <v>11</v>
@@ -2199,10 +2199,10 @@
         <v>17.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>700</v>
@@ -2211,19 +2211,19 @@
         <v>85</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
         <v>7</v>
@@ -2235,10 +2235,10 @@
         <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
         <v>10</v>
@@ -2247,38 +2247,38 @@
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AY9" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA9" t="n">
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="BC9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BD9" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BE9" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BG9" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G10" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>2.96</v>
@@ -2336,10 +2336,10 @@
         <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
         <v>2.56</v>
@@ -2348,64 +2348,64 @@
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
         <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI10" t="n">
         <v>500</v>
       </c>
-      <c r="AB10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY10" t="n">
         <v>10</v>
       </c>
-      <c r="AS10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF10" t="n">
         <v>13</v>
       </c>
-      <c r="BD10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="n">
-        <v>540</v>
+        <v>980</v>
       </c>
       <c r="AA11" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AE11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH11" t="n">
         <v>30</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AS11" t="n">
         <v>60</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
         <v>25</v>
       </c>
       <c r="BA11" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="G12" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AE12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM12" t="n">
         <v>180</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AN12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU12" t="n">
         <v>8.4</v>
       </c>
-      <c r="AG12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AV12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC12" t="n">
         <v>16.5</v>
       </c>
-      <c r="AW12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>15</v>
-      </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="I13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>1.57</v>
@@ -2915,13 +2915,13 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q13" t="n">
         <v>2.52</v>
@@ -2930,19 +2930,19 @@
         <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>10.5</v>
@@ -2951,110 +2951,110 @@
         <v>6.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
         <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK13" t="n">
         <v>150</v>
       </c>
       <c r="AL13" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA13" t="n">
         <v>34</v>
       </c>
-      <c r="AY13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>27</v>
-      </c>
       <c r="BB13" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BD13" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3091,61 +3091,61 @@
         <v>1.41</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q14" t="n">
         <v>1.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
         <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
         <v>3.4</v>
       </c>
       <c r="X14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Z14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="n">
         <v>280</v>
@@ -3157,7 +3157,7 @@
         <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
         <v>110</v>
@@ -3169,10 +3169,10 @@
         <v>9.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="n">
         <v>12.5</v>
@@ -3187,34 +3187,34 @@
         <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AR14" t="n">
         <v>60</v>
       </c>
       <c r="AS14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT14" t="n">
         <v>9.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV14" t="n">
         <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AX14" t="n">
         <v>9.199999999999999</v>
@@ -3226,7 +3226,7 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB14" t="n">
         <v>11</v>
@@ -3235,10 +3235,10 @@
         <v>12.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF14" t="n">
         <v>5.1</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
         <v>2.76</v>
@@ -3303,19 +3303,19 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
         <v>2.46</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
         <v>4.8</v>
@@ -3324,7 +3324,7 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
         <v>1.43</v>
@@ -3336,7 +3336,7 @@
         <v>15.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>420</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
         <v>500</v>
@@ -3345,7 +3345,7 @@
         <v>320</v>
       </c>
       <c r="AB15" t="n">
-        <v>190</v>
+        <v>9.6</v>
       </c>
       <c r="AC15" t="n">
         <v>14</v>
@@ -3396,13 +3396,13 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AV15" t="n">
         <v>9</v>
@@ -3420,7 +3420,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>14.5</v>
@@ -3429,20 +3429,20 @@
         <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="BG15" t="n">
         <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
         <v>3.2</v>
@@ -3488,13 +3488,13 @@
         <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
         <v>3.15</v>
@@ -3503,10 +3503,10 @@
         <v>1.44</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
@@ -3515,7 +3515,7 @@
         <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U16" t="n">
         <v>1.98</v>
@@ -3530,13 +3530,13 @@
         <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA16" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB16" t="n">
         <v>9</v>
@@ -3548,7 +3548,7 @@
         <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AF16" t="n">
         <v>15</v>
@@ -3560,13 +3560,13 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ16" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AK16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
@@ -3578,10 +3578,10 @@
         <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
         <v>9.800000000000001</v>
@@ -3593,28 +3593,28 @@
         <v>50</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ16" t="n">
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB16" t="n">
         <v>32</v>
@@ -3623,7 +3623,7 @@
         <v>29</v>
       </c>
       <c r="BD16" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BE16" t="n">
         <v>30</v>
@@ -3632,11 +3632,11 @@
         <v>27</v>
       </c>
       <c r="BG16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
         <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L17" t="n">
         <v>1.67</v>
@@ -3691,13 +3691,13 @@
         <v>1.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O17" t="n">
         <v>1.64</v>
       </c>
       <c r="P17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
@@ -3709,28 +3709,28 @@
         <v>6.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U17" t="n">
         <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
         <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z17" t="n">
         <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB17" t="n">
         <v>7</v>
@@ -3739,13 +3739,13 @@
         <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG17" t="n">
         <v>14</v>
@@ -3763,13 +3763,13 @@
         <v>42</v>
       </c>
       <c r="AL17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM17" t="n">
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO17" t="n">
         <v>110</v>
@@ -3784,10 +3784,10 @@
         <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
@@ -3796,10 +3796,10 @@
         <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
         <v>12</v>
@@ -3811,26 +3811,26 @@
         <v>60</v>
       </c>
       <c r="BB17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
         <v>34</v>
       </c>
       <c r="BD17" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE17" t="n">
         <v>28</v>
       </c>
-      <c r="BE17" t="n">
-        <v>46</v>
-      </c>
       <c r="BF17" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="BG17" t="n">
         <v>40</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G18" t="n">
         <v>2.38</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
         <v>1.5</v>
@@ -3885,34 +3885,34 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
         <v>1.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
         <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X18" t="n">
         <v>17</v>
@@ -3936,10 +3936,10 @@
         <v>32</v>
       </c>
       <c r="AE18" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AG18" t="n">
         <v>50</v>
@@ -3951,7 +3951,7 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
         <v>75</v>
@@ -3969,7 +3969,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
         <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3987,10 +3987,10 @@
         <v>6.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -4002,29 +4002,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB18" t="n">
         <v>13.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BD18" t="n">
         <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.58</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.6</v>
-      </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
@@ -4085,64 +4085,64 @@
         <v>1.55</v>
       </c>
       <c r="P19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U19" t="n">
         <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
         <v>75</v>
       </c>
       <c r="AA19" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="AB19" t="n">
         <v>5.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE19" t="n">
         <v>250</v>
       </c>
       <c r="AF19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AI19" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AJ19" t="n">
         <v>14.5</v>
@@ -4157,10 +4157,10 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO19" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
         <v>8.6</v>
@@ -4172,7 +4172,7 @@
         <v>60</v>
       </c>
       <c r="AS19" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AT19" t="n">
         <v>5.1</v>
@@ -4211,14 +4211,14 @@
         <v>220</v>
       </c>
       <c r="BF19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG19" t="n">
         <v>110</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I20" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
         <v>1.59</v>
@@ -4273,7 +4273,7 @@
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
         <v>1.6</v>
@@ -4282,25 +4282,25 @@
         <v>1.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
         <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X20" t="n">
         <v>17</v>
@@ -4309,13 +4309,13 @@
         <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA20" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AC20" t="n">
         <v>7.6</v>
@@ -4324,19 +4324,19 @@
         <v>500</v>
       </c>
       <c r="AE20" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AH20" t="n">
         <v>44</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AJ20" t="n">
         <v>160</v>
@@ -4345,7 +4345,7 @@
         <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4357,19 +4357,19 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AR20" t="n">
         <v>10.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU20" t="n">
         <v>6</v>
@@ -4378,41 +4378,41 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
         <v>11.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
         <v>15</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
         <v>6.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
         <v>2.56</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I21" t="n">
         <v>4.4</v>
@@ -4458,7 +4458,7 @@
         <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L21" t="n">
         <v>1.66</v>
@@ -4467,16 +4467,16 @@
         <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P21" t="n">
         <v>1.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
         <v>1.14</v>
@@ -4497,7 +4497,7 @@
         <v>1.65</v>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y21" t="n">
         <v>20</v>
@@ -4515,7 +4515,7 @@
         <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AE21" t="n">
         <v>500</v>
@@ -4554,10 +4554,10 @@
         <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AS21" t="n">
         <v>7.2</v>
@@ -4575,10 +4575,10 @@
         <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>19.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>4.2</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
@@ -4655,40 +4655,40 @@
         <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
         <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
         <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V22" t="n">
         <v>1.89</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4697,7 +4697,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA22" t="n">
         <v>26</v>
@@ -4745,7 +4745,7 @@
         <v>22</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>6.6</v>
@@ -4778,29 +4778,29 @@
         <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE22" t="n">
         <v>110</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG22" t="n">
         <v>18.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>1.86</v>
       </c>
       <c r="G23" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
         <v>5.4</v>
@@ -4858,16 +4858,16 @@
         <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
         <v>2.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
         <v>3.85</v>
@@ -4876,19 +4876,19 @@
         <v>1.87</v>
       </c>
       <c r="U23" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V23" t="n">
         <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X23" t="n">
         <v>90</v>
       </c>
       <c r="Y23" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4900,7 +4900,7 @@
         <v>27</v>
       </c>
       <c r="AC23" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -4909,10 +4909,10 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AG23" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>1000</v>
@@ -4921,13 +4921,13 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK23" t="n">
         <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4951,16 +4951,16 @@
         <v>4.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX23" t="n">
         <v>5.6</v>
@@ -4972,7 +4972,7 @@
         <v>9.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BB23" t="n">
         <v>9</v>
@@ -4987,14 +4987,14 @@
         <v>100</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I24" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K24" t="n">
         <v>3.15</v>
@@ -5049,7 +5049,7 @@
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.53</v>
@@ -5070,25 +5070,25 @@
         <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
         <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z24" t="n">
         <v>15.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB24" t="n">
         <v>9.800000000000001</v>
@@ -5100,7 +5100,7 @@
         <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
@@ -5112,28 +5112,28 @@
         <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AK24" t="n">
         <v>120</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN24" t="n">
         <v>75</v>
       </c>
       <c r="AO24" t="n">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ24" t="n">
         <v>7.4</v>
@@ -5166,16 +5166,16 @@
         <v>19</v>
       </c>
       <c r="BA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD24" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>14</v>
       </c>
       <c r="BE24" t="n">
         <v>130</v>
@@ -5184,11 +5184,11 @@
         <v>11.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G25" t="n">
         <v>1.9</v>
       </c>
       <c r="H25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I25" t="n">
         <v>5.8</v>
@@ -5234,7 +5234,7 @@
         <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.45</v>
@@ -5249,10 +5249,10 @@
         <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
         <v>1.31</v>
@@ -5279,7 +5279,7 @@
         <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -5294,7 +5294,7 @@
         <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>700</v>
+        <v>470</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
@@ -5303,7 +5303,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI25" t="n">
         <v>700</v>
@@ -5312,10 +5312,10 @@
         <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
@@ -5330,7 +5330,7 @@
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.1</v>
-      </c>
       <c r="J26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3.15</v>
@@ -5437,7 +5437,7 @@
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O26" t="n">
         <v>1.55</v>
@@ -5446,40 +5446,40 @@
         <v>1.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R26" t="n">
         <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U26" t="n">
         <v>1.81</v>
       </c>
       <c r="V26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.48</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z26" t="n">
         <v>20</v>
       </c>
       <c r="AA26" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26" t="n">
         <v>8</v>
@@ -5491,25 +5491,25 @@
         <v>50</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
         <v>15.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="n">
         <v>80</v>
       </c>
       <c r="AJ26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL26" t="n">
         <v>500</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5527,7 +5527,7 @@
         <v>7.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS26" t="n">
         <v>18</v>
@@ -5551,32 +5551,32 @@
         <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD26" t="n">
         <v>28</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BE26" t="n">
         <v>140</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
         <v>36</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>750</v>
       </c>
       <c r="L27" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
@@ -5637,16 +5637,16 @@
         <v>1.06</v>
       </c>
       <c r="P27" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R27" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G28" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="H28" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="X28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="n">
         <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO28" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ28" t="n">
         <v>16</v>
       </c>
       <c r="AR28" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AS28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>75</v>
-      </c>
       <c r="AX28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY28" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC28" t="n">
         <v>17.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BE28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
-        <v>11.5</v>
+        <v>75</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G29" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
@@ -6010,7 +6010,7 @@
         <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L29" t="n">
         <v>1.71</v>
@@ -6019,10 +6019,10 @@
         <v>1.16</v>
       </c>
       <c r="N29" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O29" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P29" t="n">
         <v>1.43</v>
@@ -6037,19 +6037,19 @@
         <v>7.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
         <v>1.55</v>
       </c>
       <c r="V29" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y29" t="n">
         <v>13</v>
@@ -6058,31 +6058,31 @@
         <v>46</v>
       </c>
       <c r="AA29" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AB29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AC29" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE29" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI29" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ29" t="n">
         <v>22</v>
@@ -6091,22 +6091,22 @@
         <v>32</v>
       </c>
       <c r="AL29" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM29" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AN29" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO29" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="AP29" t="n">
         <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
         <v>38</v>
@@ -6115,28 +6115,28 @@
         <v>48</v>
       </c>
       <c r="AT29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU29" t="n">
         <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW29" t="n">
         <v>44</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA29" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
@@ -6145,20 +6145,20 @@
         <v>27</v>
       </c>
       <c r="BD29" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BE29" t="n">
         <v>55</v>
       </c>
       <c r="BF29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BG29" t="n">
         <v>55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -6189,46 +6189,46 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="G30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H30" t="n">
         <v>2.32</v>
       </c>
       <c r="I30" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="J30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
         <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
         <v>1.7</v>
@@ -6237,7 +6237,7 @@
         <v>2.14</v>
       </c>
       <c r="V30" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="W30" t="n">
         <v>1.42</v>
@@ -6306,7 +6306,7 @@
         <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6336,13 +6336,13 @@
         <v>4.9</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE30" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF30" t="n">
         <v>19.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-23.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="J2" t="n">
-        <v>2.74</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>100</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.8</v>
+        <v>100</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.6</v>
+        <v>100</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.6</v>
+        <v>100</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>100</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.4</v>
+        <v>100</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>1.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>3.75</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
         <v>6.4</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X3" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>500</v>
-      </c>
       <c r="AG3" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.9</v>
+        <v>220</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.1</v>
+        <v>220</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.199999999999999</v>
+        <v>220</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.08</v>
+        <v>220</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8</v>
       </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.11</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S4" t="n">
+        <v>34</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>210</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU4" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV4" t="n">
-        <v>16.5</v>
+        <v>1.46</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>1.46</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>1.46</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>1.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>1.46</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>1.46</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>1.55</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>1.46</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>1.46</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>1.37</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.5</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.58</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>27</v>
+        <v>3.8</v>
       </c>
       <c r="AC5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>590</v>
+      </c>
+      <c r="AN5" t="n">
         <v>42</v>
       </c>
-      <c r="AD5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>600</v>
-      </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.95</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.95</v>
+        <v>140</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>70</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.7</v>
+        <v>210</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.66</v>
+        <v>240</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="H6" t="n">
-        <v>2.84</v>
+        <v>3.95</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S6" t="n">
+        <v>55</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.19</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.55</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>6.6</v>
+        <v>2.68</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>170</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>330</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AX6" t="n">
         <v>19</v>
       </c>
-      <c r="AA6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AY6" t="n">
         <v>34</v>
       </c>
-      <c r="AI6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>240</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="BC6" t="n">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>410</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>8</v>
+        <v>350</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>190</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="L7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.17</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.55</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>560</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.4</v>
+        <v>2.52</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>7.8</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J8" t="n">
         <v>2.44</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>3.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE8" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL8" t="n">
         <v>34</v>
       </c>
-      <c r="AB8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AM8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG8" t="n">
         <v>29</v>
       </c>
-      <c r="AF8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>23</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>2.04</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.89</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.5</v>
+        <v>240</v>
       </c>
       <c r="AA9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
         <v>13</v>
       </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10</v>
-      </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AX9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY9" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>38</v>
       </c>
       <c r="BA9" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="BB9" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="BC9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>220</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG9" t="n">
         <v>50</v>
       </c>
-      <c r="BD9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>65</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>19</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.52</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU10" t="n">
         <v>5.1</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AV10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF10" t="n">
         <v>26</v>
       </c>
-      <c r="AA10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>13</v>
-      </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2506,167 +2506,167 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H11" t="n">
         <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>36</v>
+        <v>410</v>
       </c>
       <c r="Z11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK11" t="n">
         <v>160</v>
       </c>
-      <c r="AF11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AL11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>260</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>12.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>20</v>
       </c>
       <c r="AR11" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AS11" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>80</v>
+        <v>5.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
         <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>15</v>
       </c>
-      <c r="AK12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AR12" t="n">
-        <v>44</v>
+        <v>2.14</v>
       </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>2.14</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>2.14</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>2.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>2.14</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>2.14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>23</v>
+        <v>2.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>2.14</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>1.93</v>
       </c>
       <c r="BC12" t="n">
-        <v>16.5</v>
+        <v>3.65</v>
       </c>
       <c r="BD12" t="n">
-        <v>38</v>
+        <v>2.08</v>
       </c>
       <c r="BE12" t="n">
-        <v>42</v>
+        <v>2.14</v>
       </c>
       <c r="BF12" t="n">
-        <v>10.5</v>
+        <v>1.97</v>
       </c>
       <c r="BG12" t="n">
-        <v>13</v>
+        <v>2.14</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2891,88 +2891,88 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
         <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
         <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AC13" t="n">
         <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH13" t="n">
         <v>28</v>
@@ -2981,80 +2981,80 @@
         <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AK13" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AL13" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AN13" t="n">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="AO13" t="n">
         <v>21</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>36</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>150</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>95</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE13" t="n">
         <v>22</v>
       </c>
-      <c r="BA13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>46</v>
-      </c>
       <c r="BF13" t="n">
-        <v>12.5</v>
+        <v>160</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="H14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I14" t="n">
         <v>8.4</v>
       </c>
-      <c r="I14" t="n">
-        <v>9</v>
-      </c>
       <c r="J14" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Z14" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="AA14" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
         <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>960</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW14" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="BB14" t="n">
         <v>11</v>
       </c>
       <c r="BC14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE14" t="n">
         <v>85</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -3294,37 +3294,37 @@
         <v>2.98</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P15" t="n">
         <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V15" t="n">
         <v>1.43</v>
@@ -3333,116 +3333,116 @@
         <v>1.56</v>
       </c>
       <c r="X15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR15" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>320</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
+      <c r="AS15" t="n">
         <v>34</v>
       </c>
-      <c r="AH15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>450</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>450</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AT15" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BF15" t="n">
         <v>26</v>
       </c>
       <c r="BG15" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
         <v>3.25</v>
@@ -3494,55 +3494,55 @@
         <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
         <v>3.15</v>
       </c>
       <c r="O16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.44</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="n">
         <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD16" t="n">
         <v>14</v>
@@ -3551,7 +3551,7 @@
         <v>42</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -3563,22 +3563,22 @@
         <v>130</v>
       </c>
       <c r="AJ16" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN16" t="n">
         <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS16" t="n">
         <v>50</v>
@@ -3599,13 +3599,13 @@
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
@@ -3623,20 +3623,20 @@
         <v>29</v>
       </c>
       <c r="BD16" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE16" t="n">
         <v>30</v>
       </c>
       <c r="BF16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG16" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O17" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
         <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="X17" t="n">
         <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="AB17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
         <v>500</v>
       </c>
       <c r="AN17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE17" t="n">
         <v>46</v>
       </c>
-      <c r="AO17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>28</v>
-      </c>
       <c r="BF17" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BG17" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G18" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J18" t="n">
         <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.5</v>
@@ -3888,22 +3888,22 @@
         <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
         <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U18" t="n">
         <v>2.04</v>
@@ -3912,7 +3912,7 @@
         <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
         <v>17</v>
@@ -3930,7 +3930,7 @@
         <v>16</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AD18" t="n">
         <v>32</v>
@@ -3954,7 +3954,7 @@
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3963,34 +3963,34 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -3999,32 +3999,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB18" t="n">
         <v>13.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.57</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.58</v>
-      </c>
       <c r="H19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.59</v>
@@ -4082,10 +4082,10 @@
         <v>2.72</v>
       </c>
       <c r="O19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q19" t="n">
         <v>2.7</v>
@@ -4100,13 +4100,13 @@
         <v>2.72</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="X19" t="n">
         <v>9.4</v>
@@ -4115,10 +4115,10 @@
         <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
         <v>5.4</v>
@@ -4127,7 +4127,7 @@
         <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE19" t="n">
         <v>250</v>
@@ -4139,31 +4139,31 @@
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI19" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
         <v>70</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>16.5</v>
@@ -4175,25 +4175,25 @@
         <v>95</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AW19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BA19" t="n">
         <v>110</v>
@@ -4211,14 +4211,14 @@
         <v>220</v>
       </c>
       <c r="BF19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
         <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I20" t="n">
         <v>4</v>
@@ -4276,7 +4276,7 @@
         <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
         <v>1.51</v>
@@ -4285,10 +4285,10 @@
         <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
         <v>2.08</v>
@@ -4303,7 +4303,7 @@
         <v>1.65</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="n">
         <v>22</v>
@@ -4324,16 +4324,16 @@
         <v>500</v>
       </c>
       <c r="AE20" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>420</v>
@@ -4342,10 +4342,10 @@
         <v>160</v>
       </c>
       <c r="AK20" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AL20" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4357,16 +4357,16 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AR20" t="n">
         <v>10.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
         <v>6.4</v>
@@ -4378,41 +4378,41 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY20" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC20" t="n">
         <v>16</v>
       </c>
-      <c r="BA20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB20" t="n">
+      <c r="BD20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG20" t="n">
         <v>8</v>
       </c>
-      <c r="BC20" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
         <v>2.56</v>
@@ -4470,16 +4470,16 @@
         <v>2.34</v>
       </c>
       <c r="O21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="R21" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
         <v>6.2</v>
@@ -4488,7 +4488,7 @@
         <v>2.26</v>
       </c>
       <c r="U21" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
         <v>1.3</v>
@@ -4509,19 +4509,19 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
         <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AE21" t="n">
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG21" t="n">
         <v>500</v>
@@ -4554,59 +4554,59 @@
         <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR21" t="n">
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AU21" t="n">
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB21" t="n">
         <v>19.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>14</v>
       </c>
       <c r="BC21" t="n">
         <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE21" t="n">
         <v>160</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>4.2</v>
       </c>
       <c r="G22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
@@ -4667,7 +4667,7 @@
         <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
         <v>2.32</v>
@@ -4676,7 +4676,7 @@
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
         <v>1.98</v>
@@ -4694,10 +4694,10 @@
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="n">
         <v>26</v>
@@ -4733,7 +4733,7 @@
         <v>170</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -4754,53 +4754,53 @@
         <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AT22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
         <v>9.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY22" t="n">
         <v>16</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BE22" t="n">
         <v>110</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG22" t="n">
         <v>18.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>1.86</v>
       </c>
       <c r="G23" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
         <v>5.4</v>
@@ -4861,22 +4861,22 @@
         <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
         <v>2.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U23" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
         <v>1.23</v>
@@ -4891,7 +4891,7 @@
         <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -4921,7 +4921,7 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
         <v>1000</v>
@@ -4945,13 +4945,13 @@
         <v>8.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="AS23" t="n">
         <v>4.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU23" t="n">
         <v>4.9</v>
@@ -4972,7 +4972,7 @@
         <v>9.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB23" t="n">
         <v>9</v>
@@ -4990,11 +4990,11 @@
         <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
         <v>3.15</v>
@@ -5055,58 +5055,58 @@
         <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG24" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>22</v>
@@ -5115,22 +5115,22 @@
         <v>65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AK24" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AL24" t="n">
         <v>170</v>
       </c>
       <c r="AM24" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO24" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
         <v>8.199999999999999</v>
@@ -5139,56 +5139,56 @@
         <v>7.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
         <v>24</v>
       </c>
       <c r="AX24" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BB24" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="BC24" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BD24" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BE24" t="n">
         <v>130</v>
       </c>
       <c r="BF24" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
         <v>5.8</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
         <v>3.6</v>
@@ -5243,13 +5243,13 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
         <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q25" t="n">
         <v>2.1</v>
@@ -5261,13 +5261,13 @@
         <v>3.85</v>
       </c>
       <c r="T25" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U25" t="n">
         <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
         <v>2.1</v>
@@ -5285,10 +5285,10 @@
         <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>22</v>
@@ -5306,7 +5306,7 @@
         <v>38</v>
       </c>
       <c r="AI25" t="n">
-        <v>700</v>
+        <v>370</v>
       </c>
       <c r="AJ25" t="n">
         <v>21</v>
@@ -5315,7 +5315,7 @@
         <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
@@ -5333,7 +5333,7 @@
         <v>14.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AS25" t="n">
         <v>10.5</v>
@@ -5357,7 +5357,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
         <v>10</v>
@@ -5378,11 +5378,11 @@
         <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
         <v>3.15</v>
       </c>
       <c r="L26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
@@ -5440,13 +5440,13 @@
         <v>2.72</v>
       </c>
       <c r="O26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P26" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R26" t="n">
         <v>1.2</v>
@@ -5455,7 +5455,7 @@
         <v>5.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U26" t="n">
         <v>1.81</v>
@@ -5479,7 +5479,7 @@
         <v>500</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC26" t="n">
         <v>8</v>
@@ -5494,7 +5494,7 @@
         <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>36</v>
@@ -5521,13 +5521,13 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ26" t="n">
         <v>7.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
         <v>18</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H27" t="n">
         <v>1.04</v>
@@ -5625,7 +5625,7 @@
         <v>750</v>
       </c>
       <c r="L27" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
@@ -5640,16 +5640,16 @@
         <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R27" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U27" t="n">
         <v>1.11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
@@ -5825,10 +5825,10 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
         <v>1.85</v>
@@ -5843,22 +5843,22 @@
         <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X28" t="n">
         <v>13</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z28" t="n">
         <v>44</v>
@@ -5873,7 +5873,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>95</v>
@@ -5882,7 +5882,7 @@
         <v>10</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>21</v>
@@ -5891,7 +5891,7 @@
         <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK28" t="n">
         <v>21</v>
@@ -5915,25 +5915,25 @@
         <v>16</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AT28" t="n">
         <v>7.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
         <v>9.4</v>
@@ -5942,29 +5942,29 @@
         <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="BB28" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD28" t="n">
         <v>34</v>
       </c>
       <c r="BE28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BF28" t="n">
         <v>11</v>
       </c>
       <c r="BG28" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
         <v>6.4</v>
@@ -6010,7 +6010,7 @@
         <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.71</v>
@@ -6019,7 +6019,7 @@
         <v>1.16</v>
       </c>
       <c r="N29" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O29" t="n">
         <v>1.72</v>
@@ -6028,7 +6028,7 @@
         <v>1.43</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
         <v>1.14</v>
@@ -6043,13 +6043,13 @@
         <v>1.55</v>
       </c>
       <c r="V29" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W29" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y29" t="n">
         <v>13</v>
@@ -6091,7 +6091,7 @@
         <v>32</v>
       </c>
       <c r="AL29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="n">
         <v>400</v>
@@ -6100,7 +6100,7 @@
         <v>29</v>
       </c>
       <c r="AO29" t="n">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="AP29" t="n">
         <v>6.6</v>
@@ -6109,13 +6109,13 @@
         <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS29" t="n">
         <v>48</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU29" t="n">
         <v>7.6</v>
@@ -6124,7 +6124,7 @@
         <v>25</v>
       </c>
       <c r="AW29" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AX29" t="n">
         <v>8.199999999999999</v>
@@ -6136,7 +6136,7 @@
         <v>32</v>
       </c>
       <c r="BA29" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
@@ -6148,7 +6148,7 @@
         <v>70</v>
       </c>
       <c r="BE29" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="BF29" t="n">
         <v>25</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -6189,76 +6189,76 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I30" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K30" t="n">
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T30" t="n">
         <v>1.7</v>
       </c>
       <c r="U30" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W30" t="n">
         <v>1.42</v>
       </c>
       <c r="X30" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z30" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y30" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>21</v>
-      </c>
       <c r="AA30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
         <v>13</v>
@@ -6270,46 +6270,46 @@
         <v>26</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH30" t="n">
         <v>18</v>
       </c>
       <c r="AI30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK30" t="n">
         <v>40</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>36</v>
       </c>
       <c r="AL30" t="n">
         <v>50</v>
       </c>
       <c r="AM30" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AO30" t="n">
         <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR30" t="n">
         <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU30" t="n">
         <v>6.8</v>
@@ -6330,29 +6330,29 @@
         <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>28</v>
+        <v>5.1</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD30" t="n">
         <v>5.2</v>
       </c>
-      <c r="BD30" t="n">
-        <v>5</v>
-      </c>
       <c r="BE30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF30" t="n">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG30" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
